--- a/data/september strat simulation/latest(for stakeholder)/strat1254_obs/result_20261007_164841(VN_strat1254_obs_07Oct).xlsx
+++ b/data/september strat simulation/latest(for stakeholder)/strat1254_obs/result_20261007_164841(VN_strat1254_obs_07Oct).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\september strat simulation\latest(for stakeholder)\strat1254_obs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDD9030-CBAF-4971-A6F2-11D091C8CE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80855E9-F8C8-4A46-9333-47413C9E552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="query" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="unique_user info" sheetId="2" r:id="rId3"/>
     <sheet name="reporting" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results export'!$A$1:$Q$202</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="402">
   <si>
     <t>traceid</t>
   </si>
@@ -1323,18 +1326,103 @@
   <si>
     <t>TP/FP</t>
   </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>protest?</t>
+  </si>
+  <si>
+    <t>preic</t>
+  </si>
+  <si>
+    <t>hit_count(order)</t>
+  </si>
+  <si>
+    <t>hit_count(user)</t>
+  </si>
+  <si>
+    <t>hit_rate(order)%</t>
+  </si>
+  <si>
+    <t>hit_rate(user)%</t>
+  </si>
+  <si>
+    <t>Account level</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Strategy Observation</t>
+  </si>
+  <si>
+    <t>True Positives (Accounts)</t>
+  </si>
+  <si>
+    <t>False Positives (Accounts)</t>
+  </si>
+  <si>
+    <t>Account Precision</t>
+  </si>
+  <si>
+    <t>Order level</t>
+  </si>
+  <si>
+    <t>Hit Rate (%)</t>
+  </si>
+  <si>
+    <t>Hit Count (Orders)</t>
+  </si>
+  <si>
+    <t>True Positives (Orders)</t>
+  </si>
+  <si>
+    <t>False Positives (Orders)</t>
+  </si>
+  <si>
+    <t>Order Precision</t>
+  </si>
+  <si>
+    <t>80.00% (12 / 15)</t>
+  </si>
+  <si>
+    <t>85.57% (172 / 201)</t>
+  </si>
+  <si>
+    <t>0.00253%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="170" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1361,7 +1449,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1429,30 +1517,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1931,28 +2078,28 @@
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2">
         <v>0.14371002132196101</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2">
         <v>337</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2">
         <v>2350</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2">
         <v>0.890625</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2">
         <v>8200826</v>
       </c>
       <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2">
         <v>922514082</v>
       </c>
       <c r="K2" t="s">
@@ -1984,28 +2131,28 @@
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3">
         <v>0.14371002132196101</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3">
         <v>337</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3">
         <v>2350</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3">
         <v>0.89230769230769202</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3">
         <v>8200826</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3">
         <v>922514082</v>
       </c>
       <c r="K3" t="s">
@@ -2037,28 +2184,28 @@
       <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4">
         <v>0.14371002132196101</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4">
         <v>337</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4">
         <v>2350</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4">
         <v>0.87878787878787801</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4">
         <v>8200826</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4">
         <v>922514082</v>
       </c>
       <c r="K4" t="s">
@@ -2090,28 +2237,28 @@
       <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5">
         <v>0.14371002132196101</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5">
         <v>337</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5">
         <v>2350</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5">
         <v>0.87878787878787801</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5">
         <v>8200826</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5">
         <v>922514082</v>
       </c>
       <c r="K5" t="s">
@@ -2143,28 +2290,28 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6">
         <v>0.14371002132196101</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6">
         <v>337</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6">
         <v>2350</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6">
         <v>0.86567164179104406</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6">
         <v>8200826</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6">
         <v>922514082</v>
       </c>
       <c r="K6" t="s">
@@ -2196,28 +2343,28 @@
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="9">
-        <v>22</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
         <v>0.91666666666666596</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7">
         <v>44465314</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
@@ -2249,28 +2396,28 @@
       <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8">
         <v>0.143098353735753</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8">
         <v>339</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8">
         <v>2351</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8">
         <v>0.77272727272727204</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8">
         <v>8200826</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8">
         <v>922514082</v>
       </c>
       <c r="K8" t="s">
@@ -2302,28 +2449,28 @@
       <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9">
         <v>0.143098353735753</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9">
         <v>339</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9">
         <v>2351</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9">
         <v>0.76404494382022403</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9">
         <v>8200826</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9">
         <v>922514082</v>
       </c>
       <c r="K9" t="s">
@@ -2355,28 +2502,28 @@
       <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10">
         <v>0.143098353735753</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10">
         <v>339</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10">
         <v>2351</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10">
         <v>0.75555555555555498</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10">
         <v>8200826</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10">
         <v>922514082</v>
       </c>
       <c r="K10" t="s">
@@ -2408,28 +2555,28 @@
       <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11">
         <v>0.143098353735753</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11">
         <v>339</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11">
         <v>2351</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11">
         <v>0.82926829268292601</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11">
         <v>8200826</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11">
         <v>922514082</v>
       </c>
       <c r="K11" t="s">
@@ -2461,28 +2608,28 @@
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12">
         <v>0.143098353735753</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12">
         <v>339</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12">
         <v>2351</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12">
         <v>0.81927710843373402</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12">
         <v>8200826</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12">
         <v>922514082</v>
       </c>
       <c r="K12" t="s">
@@ -2514,28 +2661,28 @@
       <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="9">
-        <v>1</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
         <v>45055754</v>
       </c>
       <c r="I13" t="s">
         <v>20</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
@@ -2567,28 +2714,28 @@
       <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="9">
-        <v>1</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <v>45055754</v>
       </c>
       <c r="I14" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
@@ -2620,28 +2767,28 @@
       <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="9">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="9">
-        <v>1</v>
-      </c>
-      <c r="G15" s="9">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9">
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>45055754</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
@@ -2673,28 +2820,28 @@
       <c r="B16" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="9">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>45055754</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
@@ -2726,28 +2873,28 @@
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="9">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="9">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>45055754</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="s">
@@ -2779,28 +2926,28 @@
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="9">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="9">
-        <v>1</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <v>45055754</v>
       </c>
       <c r="I18" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
@@ -2832,28 +2979,28 @@
       <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="9">
-        <v>0</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="9">
-        <v>1</v>
-      </c>
-      <c r="G19" s="9">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <v>45055754</v>
       </c>
       <c r="I19" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
@@ -2885,28 +3032,28 @@
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9">
-        <v>0</v>
-      </c>
-      <c r="D20" s="9">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="9">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9">
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <v>45055754</v>
       </c>
       <c r="I20" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
@@ -2938,28 +3085,28 @@
       <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="9">
-        <v>0</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="9">
-        <v>1</v>
-      </c>
-      <c r="G21" s="9">
-        <v>0</v>
-      </c>
-      <c r="H21" s="9">
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>45055754</v>
       </c>
       <c r="I21" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
@@ -2991,28 +3138,28 @@
       <c r="B22" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="9">
-        <v>0</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
         <v>0</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="9">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>45055754</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
@@ -3044,28 +3191,28 @@
       <c r="B23" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="9">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
         <v>0</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="9">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9">
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>45055754</v>
       </c>
       <c r="I23" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
@@ -3097,28 +3244,28 @@
       <c r="B24" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="9">
-        <v>0</v>
-      </c>
-      <c r="D24" s="9">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
         <v>0</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="9">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
         <v>45055754</v>
       </c>
       <c r="I24" t="s">
         <v>20</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
@@ -3150,28 +3297,28 @@
       <c r="B25" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="9">
-        <v>0</v>
-      </c>
-      <c r="D25" s="9">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="9">
-        <v>1</v>
-      </c>
-      <c r="G25" s="9">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9">
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
         <v>45055754</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
@@ -3203,28 +3350,28 @@
       <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="9">
-        <v>0</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>0</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
-      <c r="F26" s="9">
-        <v>1</v>
-      </c>
-      <c r="G26" s="9">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
         <v>45055754</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
@@ -3256,28 +3403,28 @@
       <c r="B27" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="9">
-        <v>0</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="9">
-        <v>1</v>
-      </c>
-      <c r="G27" s="9">
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
         <v>0.38461538461538403</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27">
         <v>45042918</v>
       </c>
       <c r="I27" t="s">
         <v>20</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
@@ -3309,28 +3456,28 @@
       <c r="B28" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28">
         <v>0.144568006843455</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28">
         <v>338</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28">
         <v>2349</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28">
         <v>0.83606557377049096</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28">
         <v>8200826</v>
       </c>
       <c r="I28" t="s">
         <v>20</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28">
         <v>922514082</v>
       </c>
       <c r="K28" t="s">
@@ -3362,28 +3509,28 @@
       <c r="B29" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29">
         <v>2</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29">
         <v>0.26041666666666602</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29">
         <v>44986521</v>
       </c>
       <c r="I29" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
@@ -3415,28 +3562,28 @@
       <c r="B30" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30">
         <v>2</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30">
         <v>0.25906735751295301</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30">
         <v>44986521</v>
       </c>
       <c r="I30" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
@@ -3468,28 +3615,28 @@
       <c r="B31" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="9">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31">
         <v>17</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31">
         <v>0.97156398104265396</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31">
         <v>44464690</v>
       </c>
       <c r="I31" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31">
         <v>1332325685</v>
       </c>
       <c r="K31" t="s">
@@ -3521,28 +3668,28 @@
       <c r="B32" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="9">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9">
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32">
         <v>17</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32">
         <v>0.96698113207547098</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32">
         <v>44464690</v>
       </c>
       <c r="I32" t="s">
         <v>20</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32">
         <v>1332325685</v>
       </c>
       <c r="K32" t="s">
@@ -3574,28 +3721,28 @@
       <c r="B33" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="9">
-        <v>1</v>
-      </c>
-      <c r="G33" s="9">
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
         <v>0.108108108108108</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33">
         <v>44986521</v>
       </c>
       <c r="I33" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="s">
@@ -3627,28 +3774,28 @@
       <c r="B34" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="9">
-        <v>1</v>
-      </c>
-      <c r="G34" s="9">
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
         <v>0.107142857142857</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34">
         <v>44986521</v>
       </c>
       <c r="I34" t="s">
         <v>20</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
@@ -3680,28 +3827,28 @@
       <c r="B35" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="9">
-        <v>1</v>
-      </c>
-      <c r="G35" s="9">
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
         <v>0.106194690265486</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35">
         <v>44986521</v>
       </c>
       <c r="I35" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
@@ -3733,28 +3880,28 @@
       <c r="B36" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36">
         <v>1</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="9">
-        <v>1</v>
-      </c>
-      <c r="G36" s="9">
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
         <v>0.105263157894736</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36">
         <v>44986521</v>
       </c>
       <c r="I36" t="s">
         <v>20</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
@@ -3786,28 +3933,28 @@
       <c r="B37" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37">
         <v>1</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
       </c>
-      <c r="F37" s="9">
-        <v>1</v>
-      </c>
-      <c r="G37" s="9">
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
         <v>0.104347826086956</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37">
         <v>44986521</v>
       </c>
       <c r="I37" t="s">
         <v>20</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
@@ -3839,28 +3986,28 @@
       <c r="B38" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
       </c>
-      <c r="F38" s="9">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9">
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
         <v>0.10344827586206801</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38">
         <v>44986521</v>
       </c>
       <c r="I38" t="s">
         <v>20</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
@@ -3892,28 +4039,28 @@
       <c r="B39" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
       </c>
-      <c r="F39" s="9">
-        <v>1</v>
-      </c>
-      <c r="G39" s="9">
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
         <v>0.10256410256410201</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39">
         <v>44986521</v>
       </c>
       <c r="I39" t="s">
         <v>20</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39">
         <v>0</v>
       </c>
       <c r="K39" t="s">
@@ -3945,28 +4092,28 @@
       <c r="B40" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40">
         <v>2</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40">
         <v>2</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40">
         <v>0.27624309392265101</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40">
         <v>44986521</v>
       </c>
       <c r="I40" t="s">
         <v>20</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" t="s">
@@ -3998,28 +4145,28 @@
       <c r="B41" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41">
         <v>2</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41">
         <v>2</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41">
         <v>0.27472527472527403</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41">
         <v>44986521</v>
       </c>
       <c r="I41" t="s">
         <v>20</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
@@ -4051,28 +4198,28 @@
       <c r="B42" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42">
         <v>2</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42">
         <v>2</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42">
         <v>0.27322404371584702</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42">
         <v>44986521</v>
       </c>
       <c r="I42" t="s">
         <v>20</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42">
         <v>0</v>
       </c>
       <c r="K42" t="s">
@@ -4104,28 +4251,28 @@
       <c r="B43" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43">
         <v>2</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43">
         <v>2</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43">
         <v>0.27173913043478198</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43">
         <v>44986521</v>
       </c>
       <c r="I43" t="s">
         <v>20</v>
       </c>
-      <c r="J43" s="9">
+      <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" t="s">
@@ -4157,28 +4304,28 @@
       <c r="B44" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44">
         <v>2</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44">
         <v>2</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44">
         <v>0.27027027027027001</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44">
         <v>44986521</v>
       </c>
       <c r="I44" t="s">
         <v>20</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
@@ -4210,28 +4357,28 @@
       <c r="B45" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45">
         <v>2</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45">
         <v>2</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45">
         <v>0.26881720430107497</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45">
         <v>44986521</v>
       </c>
       <c r="I45" t="s">
         <v>20</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
@@ -4263,28 +4410,28 @@
       <c r="B46" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46">
         <v>2</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46">
         <v>2</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46">
         <v>0.26737967914438499</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46">
         <v>44986521</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46">
         <v>0</v>
       </c>
       <c r="K46" t="s">
@@ -4316,28 +4463,28 @@
       <c r="B47" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47">
         <v>1</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
-      <c r="F47" s="9">
-        <v>1</v>
-      </c>
-      <c r="G47" s="9">
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
         <v>0.11764705882352899</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47">
         <v>44986521</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47">
         <v>0</v>
       </c>
       <c r="K47" t="s">
@@ -4369,28 +4516,28 @@
       <c r="B48" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48">
         <v>1</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
-      <c r="F48" s="9">
-        <v>1</v>
-      </c>
-      <c r="G48" s="9">
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
         <v>0.116504854368932</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48">
         <v>44986521</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" t="s">
@@ -4422,28 +4569,28 @@
       <c r="B49" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49">
         <v>1</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
-      <c r="F49" s="9">
-        <v>1</v>
-      </c>
-      <c r="G49" s="9">
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49">
         <v>0.115384615384615</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49">
         <v>44986521</v>
       </c>
       <c r="I49" t="s">
         <v>20</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
@@ -4475,28 +4622,28 @@
       <c r="B50" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50">
         <v>1</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
-      <c r="F50" s="9">
-        <v>1</v>
-      </c>
-      <c r="G50" s="9">
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
         <v>0.114285714285714</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50">
         <v>44986521</v>
       </c>
       <c r="I50" t="s">
         <v>20</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
@@ -4528,28 +4675,28 @@
       <c r="B51" t="s">
         <v>18</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51">
         <v>1</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
-      <c r="F51" s="9">
-        <v>1</v>
-      </c>
-      <c r="G51" s="9">
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
         <v>0.113207547169811</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51">
         <v>44986521</v>
       </c>
       <c r="I51" t="s">
         <v>20</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51">
         <v>0</v>
       </c>
       <c r="K51" t="s">
@@ -4581,28 +4728,28 @@
       <c r="B52" t="s">
         <v>18</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52">
         <v>1</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
-      <c r="F52" s="9">
-        <v>1</v>
-      </c>
-      <c r="G52" s="9">
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
         <v>0.11214953271028</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52">
         <v>44986521</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J52">
         <v>0</v>
       </c>
       <c r="K52" t="s">
@@ -4634,28 +4781,28 @@
       <c r="B53" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53">
         <v>1</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
-      <c r="F53" s="9">
-        <v>1</v>
-      </c>
-      <c r="G53" s="9">
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
         <v>0.11111111111111099</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53">
         <v>44986521</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53">
         <v>0</v>
       </c>
       <c r="K53" t="s">
@@ -4687,28 +4834,28 @@
       <c r="B54" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54">
         <v>1</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="9">
-        <v>1</v>
-      </c>
-      <c r="G54" s="9">
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
         <v>0.11009174311926601</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54">
         <v>44986521</v>
       </c>
       <c r="I54" t="s">
         <v>20</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" t="s">
@@ -4740,28 +4887,28 @@
       <c r="B55" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55">
         <v>1</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
-      <c r="F55" s="9">
-        <v>1</v>
-      </c>
-      <c r="G55" s="9">
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
         <v>0.109090909090909</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55">
         <v>44986521</v>
       </c>
       <c r="I55" t="s">
         <v>20</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J55">
         <v>0</v>
       </c>
       <c r="K55" t="s">
@@ -4793,28 +4940,28 @@
       <c r="B56" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56">
         <v>0.145770065075921</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56">
         <v>336</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56">
         <v>2344</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56">
         <v>1.13953488372093</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56">
         <v>8200826</v>
       </c>
       <c r="I56" t="s">
         <v>20</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J56">
         <v>922514082</v>
       </c>
       <c r="K56" t="s">
@@ -4846,28 +4993,28 @@
       <c r="B57" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="9">
-        <v>0</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57">
         <v>5</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57">
         <v>0.57142857142857095</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57">
         <v>44795713</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57">
         <v>0</v>
       </c>
       <c r="K57" t="s">
@@ -4899,28 +5046,28 @@
       <c r="B58" t="s">
         <v>18</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58">
         <v>0.15812431842966099</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58">
         <v>145</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58">
         <v>690</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58">
         <v>0.837209302325581</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58">
         <v>28625427</v>
       </c>
       <c r="I58" t="s">
         <v>20</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J58">
         <v>1192123022</v>
       </c>
       <c r="K58" t="s">
@@ -4952,28 +5099,28 @@
       <c r="B59" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59">
         <v>1</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
-      <c r="F59" s="9">
-        <v>1</v>
-      </c>
-      <c r="G59" s="9">
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
         <v>0.13953488372093001</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59">
         <v>44986521</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" t="s">
@@ -5005,28 +5152,28 @@
       <c r="B60" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60">
         <v>1</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
-      <c r="F60" s="9">
-        <v>1</v>
-      </c>
-      <c r="G60" s="9">
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
         <v>0.13793103448275801</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60">
         <v>44986521</v>
       </c>
       <c r="I60" t="s">
         <v>20</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60">
         <v>0</v>
       </c>
       <c r="K60" t="s">
@@ -5058,28 +5205,28 @@
       <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61">
         <v>1</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
-      <c r="F61" s="9">
-        <v>1</v>
-      </c>
-      <c r="G61" s="9">
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
         <v>0.13636363636363599</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61">
         <v>44986521</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J61">
         <v>0</v>
       </c>
       <c r="K61" t="s">
@@ -5111,28 +5258,28 @@
       <c r="B62" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62">
         <v>0.14513350559862101</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62">
         <v>337</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62">
         <v>2347</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62">
         <v>0.65116279069767402</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62">
         <v>8200826</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
       </c>
-      <c r="J62" s="9">
+      <c r="J62">
         <v>922514082</v>
       </c>
       <c r="K62" t="s">
@@ -5164,28 +5311,28 @@
       <c r="B63" t="s">
         <v>18</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63">
         <v>2</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63">
         <v>0.290697674418604</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63">
         <v>44986521</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
       </c>
-      <c r="J63" s="9">
+      <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" t="s">
@@ -5217,28 +5364,28 @@
       <c r="B64" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64">
         <v>2</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64">
         <v>0.28901734104046201</v>
       </c>
-      <c r="H64" s="9">
+      <c r="H64">
         <v>44986521</v>
       </c>
       <c r="I64" t="s">
         <v>20</v>
       </c>
-      <c r="J64" s="9">
+      <c r="J64">
         <v>0</v>
       </c>
       <c r="K64" t="s">
@@ -5270,28 +5417,28 @@
       <c r="B65" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C65">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65">
         <v>2</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65">
         <v>2</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65">
         <v>0.28735632183908</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65">
         <v>44986521</v>
       </c>
       <c r="I65" t="s">
         <v>20</v>
       </c>
-      <c r="J65" s="9">
+      <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" t="s">
@@ -5323,28 +5470,28 @@
       <c r="B66" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66">
         <v>2</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66">
         <v>2</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66">
         <v>0.28571428571428498</v>
       </c>
-      <c r="H66" s="9">
+      <c r="H66">
         <v>44986521</v>
       </c>
       <c r="I66" t="s">
         <v>20</v>
       </c>
-      <c r="J66" s="9">
+      <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
@@ -5376,28 +5523,28 @@
       <c r="B67" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C67">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67">
         <v>2</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67">
         <v>2</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67">
         <v>0.28409090909090901</v>
       </c>
-      <c r="H67" s="9">
+      <c r="H67">
         <v>44986521</v>
       </c>
       <c r="I67" t="s">
         <v>20</v>
       </c>
-      <c r="J67" s="9">
+      <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
@@ -5429,28 +5576,28 @@
       <c r="B68" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68">
         <v>1</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
-      <c r="F68" s="9">
-        <v>1</v>
-      </c>
-      <c r="G68" s="9">
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
         <v>8.4507042253521097E-2</v>
       </c>
-      <c r="H68" s="9">
+      <c r="H68">
         <v>44986521</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
       </c>
-      <c r="J68" s="9">
+      <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
@@ -5482,28 +5629,28 @@
       <c r="B69" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D69" s="9">
+      <c r="D69">
         <v>1</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
       </c>
-      <c r="F69" s="9">
-        <v>1</v>
-      </c>
-      <c r="G69" s="9">
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
         <v>8.3916083916083906E-2</v>
       </c>
-      <c r="H69" s="9">
+      <c r="H69">
         <v>44986521</v>
       </c>
       <c r="I69" t="s">
         <v>20</v>
       </c>
-      <c r="J69" s="9">
+      <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
@@ -5535,28 +5682,28 @@
       <c r="B70" t="s">
         <v>18</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70">
         <v>1</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
       </c>
-      <c r="F70" s="9">
-        <v>1</v>
-      </c>
-      <c r="G70" s="9">
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="H70" s="9">
+      <c r="H70">
         <v>44986521</v>
       </c>
       <c r="I70" t="s">
         <v>20</v>
       </c>
-      <c r="J70" s="9">
+      <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" t="s">
@@ -5588,28 +5735,28 @@
       <c r="B71" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D71" s="9">
+      <c r="D71">
         <v>1</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
-      <c r="F71" s="9">
-        <v>1</v>
-      </c>
-      <c r="G71" s="9">
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
         <v>8.2758620689655102E-2</v>
       </c>
-      <c r="H71" s="9">
+      <c r="H71">
         <v>44986521</v>
       </c>
       <c r="I71" t="s">
         <v>20</v>
       </c>
-      <c r="J71" s="9">
+      <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" t="s">
@@ -5641,28 +5788,28 @@
       <c r="B72" t="s">
         <v>18</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72">
         <v>1</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
       </c>
-      <c r="F72" s="9">
-        <v>1</v>
-      </c>
-      <c r="G72" s="9">
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
         <v>8.2191780821917804E-2</v>
       </c>
-      <c r="H72" s="9">
+      <c r="H72">
         <v>44986521</v>
       </c>
       <c r="I72" t="s">
         <v>20</v>
       </c>
-      <c r="J72" s="9">
+      <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
@@ -5694,28 +5841,28 @@
       <c r="B73" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="9">
+      <c r="C73">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D73" s="9">
+      <c r="D73">
         <v>1</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
-      <c r="F73" s="9">
-        <v>1</v>
-      </c>
-      <c r="G73" s="9">
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
         <v>8.16326530612244E-2</v>
       </c>
-      <c r="H73" s="9">
+      <c r="H73">
         <v>44986521</v>
       </c>
       <c r="I73" t="s">
         <v>20</v>
       </c>
-      <c r="J73" s="9">
+      <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
@@ -5747,28 +5894,28 @@
       <c r="B74" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74">
         <v>1</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
-      <c r="F74" s="9">
-        <v>1</v>
-      </c>
-      <c r="G74" s="9">
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
         <v>8.1081081081081002E-2</v>
       </c>
-      <c r="H74" s="9">
+      <c r="H74">
         <v>44986521</v>
       </c>
       <c r="I74" t="s">
         <v>20</v>
       </c>
-      <c r="J74" s="9">
+      <c r="J74">
         <v>0</v>
       </c>
       <c r="K74" t="s">
@@ -5800,28 +5947,28 @@
       <c r="B75" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75">
         <v>1</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
       </c>
-      <c r="F75" s="9">
-        <v>1</v>
-      </c>
-      <c r="G75" s="9">
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
         <v>8.0536912751677805E-2</v>
       </c>
-      <c r="H75" s="9">
+      <c r="H75">
         <v>44986521</v>
       </c>
       <c r="I75" t="s">
         <v>20</v>
       </c>
-      <c r="J75" s="9">
+      <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" t="s">
@@ -5853,28 +6000,28 @@
       <c r="B76" t="s">
         <v>18</v>
       </c>
-      <c r="C76" s="9">
-        <v>0</v>
-      </c>
-      <c r="D76" s="9">
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76">
         <v>16</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76">
         <v>0.93627450980392102</v>
       </c>
-      <c r="H76" s="9">
+      <c r="H76">
         <v>44464690</v>
       </c>
       <c r="I76" t="s">
         <v>20</v>
       </c>
-      <c r="J76" s="9">
+      <c r="J76">
         <v>1332325685</v>
       </c>
       <c r="K76" t="s">
@@ -5906,28 +6053,28 @@
       <c r="B77" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77">
         <v>0.10256410256410201</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77">
         <v>4</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77">
         <v>12</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77">
         <v>0.57499999999999996</v>
       </c>
-      <c r="H77" s="9">
+      <c r="H77">
         <v>44643928</v>
       </c>
       <c r="I77" t="s">
         <v>20</v>
       </c>
-      <c r="J77" s="9">
+      <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" t="s">
@@ -5959,28 +6106,28 @@
       <c r="B78" t="s">
         <v>18</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78">
         <v>0.10256410256410201</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78">
         <v>4</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78">
         <v>12</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78">
         <v>0.56097560975609695</v>
       </c>
-      <c r="H78" s="9">
+      <c r="H78">
         <v>44643928</v>
       </c>
       <c r="I78" t="s">
         <v>20</v>
       </c>
-      <c r="J78" s="9">
+      <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" t="s">
@@ -6012,28 +6159,28 @@
       <c r="B79" t="s">
         <v>18</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79">
         <v>0.16666666666666599</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79">
         <v>3</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79">
         <v>35</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79">
         <v>0.625</v>
       </c>
-      <c r="H79" s="9">
+      <c r="H79">
         <v>44003760</v>
       </c>
       <c r="I79" t="s">
         <v>20</v>
       </c>
-      <c r="J79" s="9">
+      <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" t="s">
@@ -6065,28 +6212,28 @@
       <c r="B80" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
       </c>
-      <c r="F80" s="9">
-        <v>1</v>
-      </c>
-      <c r="G80" s="9">
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
         <v>0.13483146067415699</v>
       </c>
-      <c r="H80" s="9">
+      <c r="H80">
         <v>44986521</v>
       </c>
       <c r="I80" t="s">
         <v>20</v>
       </c>
-      <c r="J80" s="9">
+      <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" t="s">
@@ -6118,28 +6265,28 @@
       <c r="B81" t="s">
         <v>18</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81">
         <v>1</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
-      <c r="F81" s="9">
-        <v>1</v>
-      </c>
-      <c r="G81" s="9">
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
         <v>0.133333333333333</v>
       </c>
-      <c r="H81" s="9">
+      <c r="H81">
         <v>44986521</v>
       </c>
       <c r="I81" t="s">
         <v>20</v>
       </c>
-      <c r="J81" s="9">
+      <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
@@ -6171,28 +6318,28 @@
       <c r="B82" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82">
         <v>1</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
       </c>
-      <c r="F82" s="9">
-        <v>1</v>
-      </c>
-      <c r="G82" s="9">
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
         <v>0.13186813186813101</v>
       </c>
-      <c r="H82" s="9">
+      <c r="H82">
         <v>44986521</v>
       </c>
       <c r="I82" t="s">
         <v>20</v>
       </c>
-      <c r="J82" s="9">
+      <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
@@ -6224,28 +6371,28 @@
       <c r="B83" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83">
         <v>1</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
       </c>
-      <c r="F83" s="9">
-        <v>1</v>
-      </c>
-      <c r="G83" s="9">
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
         <v>0.13043478260869501</v>
       </c>
-      <c r="H83" s="9">
+      <c r="H83">
         <v>44986521</v>
       </c>
       <c r="I83" t="s">
         <v>20</v>
       </c>
-      <c r="J83" s="9">
+      <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" t="s">
@@ -6277,28 +6424,28 @@
       <c r="B84" t="s">
         <v>18</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84">
         <v>1</v>
       </c>
       <c r="E84" t="s">
         <v>19</v>
       </c>
-      <c r="F84" s="9">
-        <v>1</v>
-      </c>
-      <c r="G84" s="9">
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
         <v>0.12903225806451599</v>
       </c>
-      <c r="H84" s="9">
+      <c r="H84">
         <v>44986521</v>
       </c>
       <c r="I84" t="s">
         <v>20</v>
       </c>
-      <c r="J84" s="9">
+      <c r="J84">
         <v>0</v>
       </c>
       <c r="K84" t="s">
@@ -6330,28 +6477,28 @@
       <c r="B85" t="s">
         <v>18</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85">
         <v>1</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
       </c>
-      <c r="F85" s="9">
-        <v>1</v>
-      </c>
-      <c r="G85" s="9">
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
         <v>0.12765957446808501</v>
       </c>
-      <c r="H85" s="9">
+      <c r="H85">
         <v>44986521</v>
       </c>
       <c r="I85" t="s">
         <v>20</v>
       </c>
-      <c r="J85" s="9">
+      <c r="J85">
         <v>0</v>
       </c>
       <c r="K85" t="s">
@@ -6383,28 +6530,28 @@
       <c r="B86" t="s">
         <v>18</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86">
         <v>1</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
       </c>
-      <c r="F86" s="9">
-        <v>1</v>
-      </c>
-      <c r="G86" s="9">
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
         <v>0.12631578947368399</v>
       </c>
-      <c r="H86" s="9">
+      <c r="H86">
         <v>44986521</v>
       </c>
       <c r="I86" t="s">
         <v>20</v>
       </c>
-      <c r="J86" s="9">
+      <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
@@ -6436,28 +6583,28 @@
       <c r="B87" t="s">
         <v>18</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87">
         <v>1</v>
       </c>
       <c r="E87" t="s">
         <v>19</v>
       </c>
-      <c r="F87" s="9">
-        <v>1</v>
-      </c>
-      <c r="G87" s="9">
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
         <v>0.125</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H87">
         <v>44986521</v>
       </c>
       <c r="I87" t="s">
         <v>20</v>
       </c>
-      <c r="J87" s="9">
+      <c r="J87">
         <v>0</v>
       </c>
       <c r="K87" t="s">
@@ -6489,28 +6636,28 @@
       <c r="B88" t="s">
         <v>18</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88">
         <v>1</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
       </c>
-      <c r="F88" s="9">
-        <v>1</v>
-      </c>
-      <c r="G88" s="9">
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
         <v>0.123711340206185</v>
       </c>
-      <c r="H88" s="9">
+      <c r="H88">
         <v>44986521</v>
       </c>
       <c r="I88" t="s">
         <v>20</v>
       </c>
-      <c r="J88" s="9">
+      <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" t="s">
@@ -6542,28 +6689,28 @@
       <c r="B89" t="s">
         <v>18</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89">
         <v>1</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
       </c>
-      <c r="F89" s="9">
-        <v>1</v>
-      </c>
-      <c r="G89" s="9">
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
         <v>0.122448979591836</v>
       </c>
-      <c r="H89" s="9">
+      <c r="H89">
         <v>44986521</v>
       </c>
       <c r="I89" t="s">
         <v>20</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J89">
         <v>0</v>
       </c>
       <c r="K89" t="s">
@@ -6595,28 +6742,28 @@
       <c r="B90" t="s">
         <v>18</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90">
         <v>1</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
-      <c r="F90" s="9">
-        <v>1</v>
-      </c>
-      <c r="G90" s="9">
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
         <v>0.12121212121212099</v>
       </c>
-      <c r="H90" s="9">
+      <c r="H90">
         <v>44986521</v>
       </c>
       <c r="I90" t="s">
         <v>20</v>
       </c>
-      <c r="J90" s="9">
+      <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" t="s">
@@ -6648,28 +6795,28 @@
       <c r="B91" t="s">
         <v>18</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91">
         <v>1</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
-      <c r="F91" s="9">
-        <v>1</v>
-      </c>
-      <c r="G91" s="9">
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
         <v>0.12</v>
       </c>
-      <c r="H91" s="9">
+      <c r="H91">
         <v>44986521</v>
       </c>
       <c r="I91" t="s">
         <v>20</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J91">
         <v>0</v>
       </c>
       <c r="K91" t="s">
@@ -6701,28 +6848,28 @@
       <c r="B92" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
       </c>
-      <c r="F92" s="9">
-        <v>1</v>
-      </c>
-      <c r="G92" s="9">
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
         <v>0.118811881188118</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H92">
         <v>44986521</v>
       </c>
       <c r="I92" t="s">
         <v>20</v>
       </c>
-      <c r="J92" s="9">
+      <c r="J92">
         <v>0</v>
       </c>
       <c r="K92" t="s">
@@ -6754,28 +6901,28 @@
       <c r="B93" t="s">
         <v>18</v>
       </c>
-      <c r="C93" s="9">
-        <v>0</v>
-      </c>
-      <c r="D93" s="9">
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
         <v>0</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93">
         <v>5</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93">
         <v>0.84090909090909005</v>
       </c>
-      <c r="H93" s="9">
+      <c r="H93">
         <v>44795713</v>
       </c>
       <c r="I93" t="s">
         <v>20</v>
       </c>
-      <c r="J93" s="9">
+      <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
@@ -6807,28 +6954,28 @@
       <c r="B94" t="s">
         <v>18</v>
       </c>
-      <c r="C94" s="9">
-        <v>0</v>
-      </c>
-      <c r="D94" s="9">
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
         <v>0</v>
       </c>
       <c r="E94" t="s">
         <v>19</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94">
         <v>5</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94">
         <v>0.82222222222222197</v>
       </c>
-      <c r="H94" s="9">
+      <c r="H94">
         <v>44795713</v>
       </c>
       <c r="I94" t="s">
         <v>20</v>
       </c>
-      <c r="J94" s="9">
+      <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
@@ -6860,28 +7007,28 @@
       <c r="B95" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="9">
-        <v>0</v>
-      </c>
-      <c r="D95" s="9">
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
         <v>0</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95">
         <v>5</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95">
         <v>0.80434782608695599</v>
       </c>
-      <c r="H95" s="9">
+      <c r="H95">
         <v>44795713</v>
       </c>
       <c r="I95" t="s">
         <v>20</v>
       </c>
-      <c r="J95" s="9">
+      <c r="J95">
         <v>0</v>
       </c>
       <c r="K95" t="s">
@@ -6913,28 +7060,28 @@
       <c r="B96" t="s">
         <v>18</v>
       </c>
-      <c r="C96" s="9">
-        <v>0</v>
-      </c>
-      <c r="D96" s="9">
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
         <v>0</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96">
         <v>5</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96">
         <v>0.78723404255319096</v>
       </c>
-      <c r="H96" s="9">
+      <c r="H96">
         <v>44795713</v>
       </c>
       <c r="I96" t="s">
         <v>20</v>
       </c>
-      <c r="J96" s="9">
+      <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
@@ -6966,28 +7113,28 @@
       <c r="B97" t="s">
         <v>18</v>
       </c>
-      <c r="C97" s="9">
-        <v>0</v>
-      </c>
-      <c r="D97" s="9">
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
         <v>0</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97">
         <v>5</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97">
         <v>0.77083333333333304</v>
       </c>
-      <c r="H97" s="9">
+      <c r="H97">
         <v>44795713</v>
       </c>
       <c r="I97" t="s">
         <v>20</v>
       </c>
-      <c r="J97" s="9">
+      <c r="J97">
         <v>0</v>
       </c>
       <c r="K97" t="s">
@@ -7019,28 +7166,28 @@
       <c r="B98" t="s">
         <v>18</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98">
         <v>1</v>
       </c>
       <c r="E98" t="s">
         <v>19</v>
       </c>
-      <c r="F98" s="9">
-        <v>1</v>
-      </c>
-      <c r="G98" s="9">
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
         <v>7.3170731707316999E-2</v>
       </c>
-      <c r="H98" s="9">
+      <c r="H98">
         <v>44986521</v>
       </c>
       <c r="I98" t="s">
         <v>20</v>
       </c>
-      <c r="J98" s="9">
+      <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
@@ -7072,28 +7219,28 @@
       <c r="B99" t="s">
         <v>18</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99">
         <v>1</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
       </c>
-      <c r="F99" s="9">
-        <v>1</v>
-      </c>
-      <c r="G99" s="9">
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
         <v>7.2727272727272696E-2</v>
       </c>
-      <c r="H99" s="9">
+      <c r="H99">
         <v>44986521</v>
       </c>
       <c r="I99" t="s">
         <v>20</v>
       </c>
-      <c r="J99" s="9">
+      <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
@@ -7125,28 +7272,28 @@
       <c r="B100" t="s">
         <v>18</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100">
         <v>1</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
       </c>
-      <c r="F100" s="9">
-        <v>1</v>
-      </c>
-      <c r="G100" s="9">
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
         <v>7.2289156626505993E-2</v>
       </c>
-      <c r="H100" s="9">
+      <c r="H100">
         <v>44986521</v>
       </c>
       <c r="I100" t="s">
         <v>20</v>
       </c>
-      <c r="J100" s="9">
+      <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" t="s">
@@ -7178,28 +7325,28 @@
       <c r="B101" t="s">
         <v>18</v>
       </c>
-      <c r="C101" s="9">
-        <v>0</v>
-      </c>
-      <c r="D101" s="9">
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
         <v>0</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101">
         <v>5</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101">
         <v>0.69565217391304301</v>
       </c>
-      <c r="H101" s="9">
+      <c r="H101">
         <v>44795713</v>
       </c>
       <c r="I101" t="s">
         <v>20</v>
       </c>
-      <c r="J101" s="9">
+      <c r="J101">
         <v>0</v>
       </c>
       <c r="K101" t="s">
@@ -7231,28 +7378,28 @@
       <c r="B102" t="s">
         <v>18</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102">
         <v>2</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102">
         <v>2</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102">
         <v>0.25252525252525199</v>
       </c>
-      <c r="H102" s="9">
+      <c r="H102">
         <v>44986521</v>
       </c>
       <c r="I102" t="s">
         <v>20</v>
       </c>
-      <c r="J102" s="9">
+      <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" t="s">
@@ -7284,28 +7431,28 @@
       <c r="B103" t="s">
         <v>18</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103">
         <v>0.32288401253918497</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103">
         <v>103</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103">
         <v>396</v>
       </c>
-      <c r="G103" s="9">
-        <v>0</v>
-      </c>
-      <c r="H103" s="9">
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
         <v>34917006</v>
       </c>
       <c r="I103" t="s">
         <v>20</v>
       </c>
-      <c r="J103" s="9">
+      <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
@@ -7337,28 +7484,28 @@
       <c r="B104" t="s">
         <v>18</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104">
         <v>0.32288401253918497</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104">
         <v>103</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104">
         <v>396</v>
       </c>
-      <c r="G104" s="9">
-        <v>0</v>
-      </c>
-      <c r="H104" s="9">
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
         <v>34917006</v>
       </c>
       <c r="I104" t="s">
         <v>20</v>
       </c>
-      <c r="J104" s="9">
+      <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
@@ -7390,28 +7537,28 @@
       <c r="B105" t="s">
         <v>18</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C105">
         <v>0.14677700348431999</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105">
         <v>337</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105">
         <v>2343</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105">
         <v>0.8</v>
       </c>
-      <c r="H105" s="9">
+      <c r="H105">
         <v>8200826</v>
       </c>
       <c r="I105" t="s">
         <v>20</v>
       </c>
-      <c r="J105" s="9">
+      <c r="J105">
         <v>922514082</v>
       </c>
       <c r="K105" t="s">
@@ -7443,28 +7590,28 @@
       <c r="B106" t="s">
         <v>18</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106">
         <v>0.14677700348431999</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106">
         <v>337</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106">
         <v>2343</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106">
         <v>0.80392156862745101</v>
       </c>
-      <c r="H106" s="9">
+      <c r="H106">
         <v>8200826</v>
       </c>
       <c r="I106" t="s">
         <v>20</v>
       </c>
-      <c r="J106" s="9">
+      <c r="J106">
         <v>922514082</v>
       </c>
       <c r="K106" t="s">
@@ -7496,28 +7643,28 @@
       <c r="B107" t="s">
         <v>18</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C107">
         <v>0.18181818181818099</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107">
         <v>2</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107">
         <v>282</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107">
         <v>0.57142857142857095</v>
       </c>
-      <c r="H107" s="9">
+      <c r="H107">
         <v>37669736</v>
       </c>
       <c r="I107" t="s">
         <v>20</v>
       </c>
-      <c r="J107" s="9">
+      <c r="J107">
         <v>0</v>
       </c>
       <c r="K107" t="s">
@@ -7549,28 +7696,28 @@
       <c r="B108" t="s">
         <v>18</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108">
         <v>0.18181818181818099</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108">
         <v>2</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108">
         <v>282</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108">
         <v>0.54545454545454497</v>
       </c>
-      <c r="H108" s="9">
+      <c r="H108">
         <v>37669736</v>
       </c>
       <c r="I108" t="s">
         <v>20</v>
       </c>
-      <c r="J108" s="9">
+      <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
@@ -7602,28 +7749,28 @@
       <c r="B109" t="s">
         <v>18</v>
       </c>
-      <c r="C109" s="9">
+      <c r="C109">
         <v>0.14527320034692101</v>
       </c>
-      <c r="D109" s="9">
+      <c r="D109">
         <v>335</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109">
         <v>2345</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109">
         <v>0.78947368421052599</v>
       </c>
-      <c r="H109" s="9">
+      <c r="H109">
         <v>8200826</v>
       </c>
       <c r="I109" t="s">
         <v>20</v>
       </c>
-      <c r="J109" s="9">
+      <c r="J109">
         <v>922514082</v>
       </c>
       <c r="K109" t="s">
@@ -7655,28 +7802,28 @@
       <c r="B110" t="s">
         <v>18</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110">
         <v>0.14527320034692101</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110">
         <v>335</v>
       </c>
       <c r="E110" t="s">
         <v>19</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110">
         <v>2345</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110">
         <v>0.76923076923076905</v>
       </c>
-      <c r="H110" s="9">
+      <c r="H110">
         <v>8200826</v>
       </c>
       <c r="I110" t="s">
         <v>20</v>
       </c>
-      <c r="J110" s="9">
+      <c r="J110">
         <v>922514082</v>
       </c>
       <c r="K110" t="s">
@@ -7708,28 +7855,28 @@
       <c r="B111" t="s">
         <v>18</v>
       </c>
-      <c r="C111" s="9">
+      <c r="C111">
         <v>0.14513350559862101</v>
       </c>
-      <c r="D111" s="9">
+      <c r="D111">
         <v>337</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111">
         <v>2347</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111">
         <v>0.67346938775510201</v>
       </c>
-      <c r="H111" s="9">
+      <c r="H111">
         <v>8200826</v>
       </c>
       <c r="I111" t="s">
         <v>20</v>
       </c>
-      <c r="J111" s="9">
+      <c r="J111">
         <v>922514082</v>
       </c>
       <c r="K111" t="s">
@@ -7761,28 +7908,28 @@
       <c r="B112" t="s">
         <v>18</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112">
         <v>0.14513350559862101</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112">
         <v>337</v>
       </c>
       <c r="E112" t="s">
         <v>19</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112">
         <v>2347</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112">
         <v>0.66</v>
       </c>
-      <c r="H112" s="9">
+      <c r="H112">
         <v>8200826</v>
       </c>
       <c r="I112" t="s">
         <v>20</v>
       </c>
-      <c r="J112" s="9">
+      <c r="J112">
         <v>922514082</v>
       </c>
       <c r="K112" t="s">
@@ -7814,28 +7961,28 @@
       <c r="B113" t="s">
         <v>159</v>
       </c>
-      <c r="C113" s="9">
-        <v>0</v>
-      </c>
-      <c r="D113" s="9">
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
         <v>0</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113">
         <v>249</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113">
         <v>0.9</v>
       </c>
-      <c r="H113" s="9">
+      <c r="H113">
         <v>38375955</v>
       </c>
       <c r="I113" t="s">
         <v>20</v>
       </c>
-      <c r="J113" s="9">
+      <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
@@ -7867,28 +8014,28 @@
       <c r="B114" t="s">
         <v>18</v>
       </c>
-      <c r="C114" s="9">
-        <v>0</v>
-      </c>
-      <c r="D114" s="9">
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
         <v>0</v>
       </c>
       <c r="E114" t="s">
         <v>19</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114">
         <v>16</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114">
         <v>0.97938144329896903</v>
       </c>
-      <c r="H114" s="9">
+      <c r="H114">
         <v>44464690</v>
       </c>
       <c r="I114" t="s">
         <v>20</v>
       </c>
-      <c r="J114" s="9">
+      <c r="J114">
         <v>1332325685</v>
       </c>
       <c r="K114" t="s">
@@ -7920,28 +8067,28 @@
       <c r="B115" t="s">
         <v>18</v>
       </c>
-      <c r="C115" s="9">
-        <v>0</v>
-      </c>
-      <c r="D115" s="9">
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
         <v>0</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115">
         <v>16</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115">
         <v>0.97435897435897401</v>
       </c>
-      <c r="H115" s="9">
+      <c r="H115">
         <v>44464690</v>
       </c>
       <c r="I115" t="s">
         <v>20</v>
       </c>
-      <c r="J115" s="9">
+      <c r="J115">
         <v>1332325685</v>
       </c>
       <c r="K115" t="s">
@@ -7973,28 +8120,28 @@
       <c r="B116" t="s">
         <v>18</v>
       </c>
-      <c r="C116" s="9">
-        <v>0</v>
-      </c>
-      <c r="D116" s="9">
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
         <v>0</v>
       </c>
       <c r="E116" t="s">
         <v>19</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116">
         <v>16</v>
       </c>
-      <c r="G116" s="9">
+      <c r="G116">
         <v>0.96938775510204001</v>
       </c>
-      <c r="H116" s="9">
+      <c r="H116">
         <v>44464690</v>
       </c>
       <c r="I116" t="s">
         <v>20</v>
       </c>
-      <c r="J116" s="9">
+      <c r="J116">
         <v>1332325685</v>
       </c>
       <c r="K116" t="s">
@@ -8026,28 +8173,28 @@
       <c r="B117" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="9">
-        <v>0</v>
-      </c>
-      <c r="D117" s="9">
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
         <v>0</v>
       </c>
       <c r="E117" t="s">
         <v>19</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117">
         <v>16</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117">
         <v>0.96446700507614203</v>
       </c>
-      <c r="H117" s="9">
+      <c r="H117">
         <v>44464690</v>
       </c>
       <c r="I117" t="s">
         <v>20</v>
       </c>
-      <c r="J117" s="9">
+      <c r="J117">
         <v>1332325685</v>
       </c>
       <c r="K117" t="s">
@@ -8079,28 +8226,28 @@
       <c r="B118" t="s">
         <v>18</v>
       </c>
-      <c r="C118" s="9">
-        <v>0</v>
-      </c>
-      <c r="D118" s="9">
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
         <v>0</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F118">
         <v>16</v>
       </c>
-      <c r="G118" s="9">
+      <c r="G118">
         <v>0.959595959595959</v>
       </c>
-      <c r="H118" s="9">
+      <c r="H118">
         <v>44464690</v>
       </c>
       <c r="I118" t="s">
         <v>20</v>
       </c>
-      <c r="J118" s="9">
+      <c r="J118">
         <v>1332325685</v>
       </c>
       <c r="K118" t="s">
@@ -8132,28 +8279,28 @@
       <c r="B119" t="s">
         <v>18</v>
       </c>
-      <c r="C119" s="9">
-        <v>0</v>
-      </c>
-      <c r="D119" s="9">
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
         <v>0</v>
       </c>
       <c r="E119" t="s">
         <v>19</v>
       </c>
-      <c r="F119" s="9">
+      <c r="F119">
         <v>16</v>
       </c>
-      <c r="G119" s="9">
+      <c r="G119">
         <v>0.95477386934673303</v>
       </c>
-      <c r="H119" s="9">
+      <c r="H119">
         <v>44464690</v>
       </c>
       <c r="I119" t="s">
         <v>20</v>
       </c>
-      <c r="J119" s="9">
+      <c r="J119">
         <v>1332325685</v>
       </c>
       <c r="K119" t="s">
@@ -8185,28 +8332,28 @@
       <c r="B120" t="s">
         <v>18</v>
       </c>
-      <c r="C120" s="9">
-        <v>0</v>
-      </c>
-      <c r="D120" s="9">
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
         <v>0</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F120">
         <v>16</v>
       </c>
-      <c r="G120" s="9">
+      <c r="G120">
         <v>0.95</v>
       </c>
-      <c r="H120" s="9">
+      <c r="H120">
         <v>44464690</v>
       </c>
       <c r="I120" t="s">
         <v>20</v>
       </c>
-      <c r="J120" s="9">
+      <c r="J120">
         <v>1332325685</v>
       </c>
       <c r="K120" t="s">
@@ -8238,28 +8385,28 @@
       <c r="B121" t="s">
         <v>18</v>
       </c>
-      <c r="C121" s="9">
-        <v>0</v>
-      </c>
-      <c r="D121" s="9">
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
         <v>0</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
       </c>
-      <c r="F121" s="9">
+      <c r="F121">
         <v>16</v>
       </c>
-      <c r="G121" s="9">
+      <c r="G121">
         <v>0.94527363184079605</v>
       </c>
-      <c r="H121" s="9">
+      <c r="H121">
         <v>44464690</v>
       </c>
       <c r="I121" t="s">
         <v>20</v>
       </c>
-      <c r="J121" s="9">
+      <c r="J121">
         <v>1332325685</v>
       </c>
       <c r="K121" t="s">
@@ -8291,28 +8438,28 @@
       <c r="B122" t="s">
         <v>18</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122">
         <v>0.15812431842966099</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122">
         <v>145</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
       </c>
-      <c r="F122" s="9">
+      <c r="F122">
         <v>690</v>
       </c>
-      <c r="G122" s="9">
+      <c r="G122">
         <v>0.81578947368420995</v>
       </c>
-      <c r="H122" s="9">
+      <c r="H122">
         <v>28625427</v>
       </c>
       <c r="I122" t="s">
         <v>20</v>
       </c>
-      <c r="J122" s="9">
+      <c r="J122">
         <v>1192123022</v>
       </c>
       <c r="K122" t="s">
@@ -8344,28 +8491,28 @@
       <c r="B123" t="s">
         <v>18</v>
       </c>
-      <c r="C123" s="9">
-        <v>0</v>
-      </c>
-      <c r="D123" s="9">
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
         <v>0</v>
       </c>
       <c r="E123" t="s">
         <v>19</v>
       </c>
-      <c r="F123" s="9">
+      <c r="F123">
         <v>16</v>
       </c>
-      <c r="G123" s="9">
+      <c r="G123">
         <v>0.98453608247422597</v>
       </c>
-      <c r="H123" s="9">
+      <c r="H123">
         <v>44464690</v>
       </c>
       <c r="I123" t="s">
         <v>20</v>
       </c>
-      <c r="J123" s="9">
+      <c r="J123">
         <v>1332325685</v>
       </c>
       <c r="K123" t="s">
@@ -8397,28 +8544,28 @@
       <c r="B124" t="s">
         <v>18</v>
       </c>
-      <c r="C124" s="9">
-        <v>0</v>
-      </c>
-      <c r="D124" s="9">
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
         <v>0</v>
       </c>
       <c r="E124" t="s">
         <v>19</v>
       </c>
-      <c r="F124" s="9">
+      <c r="F124">
         <v>16</v>
       </c>
-      <c r="G124" s="9">
+      <c r="G124">
         <v>0.979487179487179</v>
       </c>
-      <c r="H124" s="9">
+      <c r="H124">
         <v>44464690</v>
       </c>
       <c r="I124" t="s">
         <v>20</v>
       </c>
-      <c r="J124" s="9">
+      <c r="J124">
         <v>1332325685</v>
       </c>
       <c r="K124" t="s">
@@ -8450,28 +8597,28 @@
       <c r="B125" t="s">
         <v>18</v>
       </c>
-      <c r="C125" s="9">
-        <v>0</v>
-      </c>
-      <c r="D125" s="9">
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
         <v>0</v>
       </c>
       <c r="E125" t="s">
         <v>19</v>
       </c>
-      <c r="F125" s="9">
+      <c r="F125">
         <v>16</v>
       </c>
-      <c r="G125" s="9">
+      <c r="G125">
         <v>0.97448979591836704</v>
       </c>
-      <c r="H125" s="9">
+      <c r="H125">
         <v>44464690</v>
       </c>
       <c r="I125" t="s">
         <v>20</v>
       </c>
-      <c r="J125" s="9">
+      <c r="J125">
         <v>1332325685</v>
       </c>
       <c r="K125" t="s">
@@ -8503,28 +8650,28 @@
       <c r="B126" t="s">
         <v>18</v>
       </c>
-      <c r="C126" s="9">
-        <v>0</v>
-      </c>
-      <c r="D126" s="9">
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
         <v>0</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
       </c>
-      <c r="F126" s="9">
+      <c r="F126">
         <v>16</v>
       </c>
-      <c r="G126" s="9">
+      <c r="G126">
         <v>0.96954314720812096</v>
       </c>
-      <c r="H126" s="9">
+      <c r="H126">
         <v>44464690</v>
       </c>
       <c r="I126" t="s">
         <v>20</v>
       </c>
-      <c r="J126" s="9">
+      <c r="J126">
         <v>1332325685</v>
       </c>
       <c r="K126" t="s">
@@ -8556,28 +8703,28 @@
       <c r="B127" t="s">
         <v>18</v>
       </c>
-      <c r="C127" s="9">
-        <v>0</v>
-      </c>
-      <c r="D127" s="9">
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
         <v>0</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
       </c>
-      <c r="F127" s="9">
+      <c r="F127">
         <v>16</v>
       </c>
-      <c r="G127" s="9">
+      <c r="G127">
         <v>0.96464646464646397</v>
       </c>
-      <c r="H127" s="9">
+      <c r="H127">
         <v>44464690</v>
       </c>
       <c r="I127" t="s">
         <v>20</v>
       </c>
-      <c r="J127" s="9">
+      <c r="J127">
         <v>1332325685</v>
       </c>
       <c r="K127" t="s">
@@ -8609,28 +8756,28 @@
       <c r="B128" t="s">
         <v>18</v>
       </c>
-      <c r="C128" s="9">
-        <v>0</v>
-      </c>
-      <c r="D128" s="9">
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
         <v>0</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
       </c>
-      <c r="F128" s="9">
+      <c r="F128">
         <v>16</v>
       </c>
-      <c r="G128" s="9">
+      <c r="G128">
         <v>0.95979899497487398</v>
       </c>
-      <c r="H128" s="9">
+      <c r="H128">
         <v>44464690</v>
       </c>
       <c r="I128" t="s">
         <v>20</v>
       </c>
-      <c r="J128" s="9">
+      <c r="J128">
         <v>1332325685</v>
       </c>
       <c r="K128" t="s">
@@ -8662,28 +8809,28 @@
       <c r="B129" t="s">
         <v>18</v>
       </c>
-      <c r="C129" s="9">
-        <v>0</v>
-      </c>
-      <c r="D129" s="9">
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
         <v>0</v>
       </c>
       <c r="E129" t="s">
         <v>19</v>
       </c>
-      <c r="F129" s="9">
+      <c r="F129">
         <v>16</v>
       </c>
-      <c r="G129" s="9">
+      <c r="G129">
         <v>0.95499999999999996</v>
       </c>
-      <c r="H129" s="9">
+      <c r="H129">
         <v>44464690</v>
       </c>
       <c r="I129" t="s">
         <v>20</v>
       </c>
-      <c r="J129" s="9">
+      <c r="J129">
         <v>1332325685</v>
       </c>
       <c r="K129" t="s">
@@ -8715,28 +8862,28 @@
       <c r="B130" t="s">
         <v>18</v>
       </c>
-      <c r="C130" s="9">
-        <v>0</v>
-      </c>
-      <c r="D130" s="9">
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
         <v>0</v>
       </c>
       <c r="E130" t="s">
         <v>19</v>
       </c>
-      <c r="F130" s="9">
+      <c r="F130">
         <v>16</v>
       </c>
-      <c r="G130" s="9">
+      <c r="G130">
         <v>0.95024875621890503</v>
       </c>
-      <c r="H130" s="9">
+      <c r="H130">
         <v>44464690</v>
       </c>
       <c r="I130" t="s">
         <v>20</v>
       </c>
-      <c r="J130" s="9">
+      <c r="J130">
         <v>1332325685</v>
       </c>
       <c r="K130" t="s">
@@ -8768,28 +8915,28 @@
       <c r="B131" t="s">
         <v>18</v>
       </c>
-      <c r="C131" s="9">
-        <v>0</v>
-      </c>
-      <c r="D131" s="9">
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
         <v>0</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
       </c>
-      <c r="F131" s="9">
+      <c r="F131">
         <v>16</v>
       </c>
-      <c r="G131" s="9">
+      <c r="G131">
         <v>0.94554455445544505</v>
       </c>
-      <c r="H131" s="9">
+      <c r="H131">
         <v>44464690</v>
       </c>
       <c r="I131" t="s">
         <v>20</v>
       </c>
-      <c r="J131" s="9">
+      <c r="J131">
         <v>1332325685</v>
       </c>
       <c r="K131" t="s">
@@ -8821,28 +8968,28 @@
       <c r="B132" t="s">
         <v>18</v>
       </c>
-      <c r="C132" s="9">
-        <v>0</v>
-      </c>
-      <c r="D132" s="9">
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
         <v>0</v>
       </c>
       <c r="E132" t="s">
         <v>19</v>
       </c>
-      <c r="F132" s="9">
+      <c r="F132">
         <v>16</v>
       </c>
-      <c r="G132" s="9">
+      <c r="G132">
         <v>0.94088669950738901</v>
       </c>
-      <c r="H132" s="9">
+      <c r="H132">
         <v>44464690</v>
       </c>
       <c r="I132" t="s">
         <v>20</v>
       </c>
-      <c r="J132" s="9">
+      <c r="J132">
         <v>1332325685</v>
       </c>
       <c r="K132" t="s">
@@ -8874,28 +9021,28 @@
       <c r="B133" t="s">
         <v>18</v>
       </c>
-      <c r="C133" s="9">
-        <v>0</v>
-      </c>
-      <c r="D133" s="9">
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
         <v>0</v>
       </c>
       <c r="E133" t="s">
         <v>19</v>
       </c>
-      <c r="F133" s="9">
+      <c r="F133">
         <v>17</v>
       </c>
-      <c r="G133" s="9">
+      <c r="G133">
         <v>0.96244131455398996</v>
       </c>
-      <c r="H133" s="9">
+      <c r="H133">
         <v>44464690</v>
       </c>
       <c r="I133" t="s">
         <v>20</v>
       </c>
-      <c r="J133" s="9">
+      <c r="J133">
         <v>1332325685</v>
       </c>
       <c r="K133" t="s">
@@ -8927,28 +9074,28 @@
       <c r="B134" t="s">
         <v>18</v>
       </c>
-      <c r="C134" s="9">
-        <v>0</v>
-      </c>
-      <c r="D134" s="9">
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
         <v>0</v>
       </c>
       <c r="E134" t="s">
         <v>19</v>
       </c>
-      <c r="F134" s="9">
+      <c r="F134">
         <v>17</v>
       </c>
-      <c r="G134" s="9">
+      <c r="G134">
         <v>0.95794392523364402</v>
       </c>
-      <c r="H134" s="9">
+      <c r="H134">
         <v>44464690</v>
       </c>
       <c r="I134" t="s">
         <v>20</v>
       </c>
-      <c r="J134" s="9">
+      <c r="J134">
         <v>1332325685</v>
       </c>
       <c r="K134" t="s">
@@ -8980,28 +9127,28 @@
       <c r="B135" t="s">
         <v>18</v>
       </c>
-      <c r="C135" s="9">
-        <v>0</v>
-      </c>
-      <c r="D135" s="9">
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
         <v>0</v>
       </c>
       <c r="E135" t="s">
         <v>19</v>
       </c>
-      <c r="F135" s="9">
+      <c r="F135">
         <v>17</v>
       </c>
-      <c r="G135" s="9">
+      <c r="G135">
         <v>0.95348837209302295</v>
       </c>
-      <c r="H135" s="9">
+      <c r="H135">
         <v>44464690</v>
       </c>
       <c r="I135" t="s">
         <v>20</v>
       </c>
-      <c r="J135" s="9">
+      <c r="J135">
         <v>1332325685</v>
       </c>
       <c r="K135" t="s">
@@ -9033,28 +9180,28 @@
       <c r="B136" t="s">
         <v>18</v>
       </c>
-      <c r="C136" s="9">
-        <v>0</v>
-      </c>
-      <c r="D136" s="9">
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
         <v>0</v>
       </c>
       <c r="E136" t="s">
         <v>19</v>
       </c>
-      <c r="F136" s="9">
+      <c r="F136">
         <v>17</v>
       </c>
-      <c r="G136" s="9">
+      <c r="G136">
         <v>0.94907407407407396</v>
       </c>
-      <c r="H136" s="9">
+      <c r="H136">
         <v>44464690</v>
       </c>
       <c r="I136" t="s">
         <v>20</v>
       </c>
-      <c r="J136" s="9">
+      <c r="J136">
         <v>1332325685</v>
       </c>
       <c r="K136" t="s">
@@ -9086,28 +9233,28 @@
       <c r="B137" t="s">
         <v>18</v>
       </c>
-      <c r="C137" s="9">
-        <v>0</v>
-      </c>
-      <c r="D137" s="9">
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
         <v>0</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
       </c>
-      <c r="F137" s="9">
+      <c r="F137">
         <v>17</v>
       </c>
-      <c r="G137" s="9">
+      <c r="G137">
         <v>0.94470046082949299</v>
       </c>
-      <c r="H137" s="9">
+      <c r="H137">
         <v>44464690</v>
       </c>
       <c r="I137" t="s">
         <v>20</v>
       </c>
-      <c r="J137" s="9">
+      <c r="J137">
         <v>1332325685</v>
       </c>
       <c r="K137" t="s">
@@ -9139,28 +9286,28 @@
       <c r="B138" t="s">
         <v>18</v>
       </c>
-      <c r="C138" s="9">
-        <v>0</v>
-      </c>
-      <c r="D138" s="9">
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
         <v>0</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
       </c>
-      <c r="F138" s="9">
+      <c r="F138">
         <v>17</v>
       </c>
-      <c r="G138" s="9">
+      <c r="G138">
         <v>0.94036697247706402</v>
       </c>
-      <c r="H138" s="9">
+      <c r="H138">
         <v>44464690</v>
       </c>
       <c r="I138" t="s">
         <v>20</v>
       </c>
-      <c r="J138" s="9">
+      <c r="J138">
         <v>1332325685</v>
       </c>
       <c r="K138" t="s">
@@ -9192,28 +9339,28 @@
       <c r="B139" t="s">
         <v>18</v>
       </c>
-      <c r="C139" s="9">
-        <v>0</v>
-      </c>
-      <c r="D139" s="9">
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
         <v>0</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
       </c>
-      <c r="F139" s="9">
+      <c r="F139">
         <v>17</v>
       </c>
-      <c r="G139" s="9">
+      <c r="G139">
         <v>0.93607305936073004</v>
       </c>
-      <c r="H139" s="9">
+      <c r="H139">
         <v>44464690</v>
       </c>
       <c r="I139" t="s">
         <v>20</v>
       </c>
-      <c r="J139" s="9">
+      <c r="J139">
         <v>1332325685</v>
       </c>
       <c r="K139" t="s">
@@ -9245,28 +9392,28 @@
       <c r="B140" t="s">
         <v>18</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140">
         <v>2.6315789473684199E-2</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140">
         <v>1</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
       </c>
-      <c r="F140" s="9">
+      <c r="F140">
         <v>164</v>
       </c>
-      <c r="G140" s="9">
-        <v>1</v>
-      </c>
-      <c r="H140" s="9">
+      <c r="G140">
+        <v>1</v>
+      </c>
+      <c r="H140">
         <v>40546651</v>
       </c>
       <c r="I140" t="s">
         <v>20</v>
       </c>
-      <c r="J140" s="9">
+      <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
@@ -9298,28 +9445,28 @@
       <c r="B141" t="s">
         <v>18</v>
       </c>
-      <c r="C141" s="9">
+      <c r="C141">
         <v>0.14513350559862101</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141">
         <v>337</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
       </c>
-      <c r="F141" s="9">
+      <c r="F141">
         <v>2347</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G141">
         <v>0.8</v>
       </c>
-      <c r="H141" s="9">
+      <c r="H141">
         <v>8200826</v>
       </c>
       <c r="I141" t="s">
         <v>20</v>
       </c>
-      <c r="J141" s="9">
+      <c r="J141">
         <v>922514082</v>
       </c>
       <c r="K141" t="s">
@@ -9351,28 +9498,28 @@
       <c r="B142" t="s">
         <v>18</v>
       </c>
-      <c r="C142" s="9">
-        <v>0</v>
-      </c>
-      <c r="D142" s="9">
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
         <v>0</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
       </c>
-      <c r="F142" s="9">
+      <c r="F142">
         <v>188</v>
       </c>
-      <c r="G142" s="9">
-        <v>0</v>
-      </c>
-      <c r="H142" s="9">
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
         <v>40007087</v>
       </c>
       <c r="I142" t="s">
         <v>20</v>
       </c>
-      <c r="J142" s="9">
+      <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
@@ -9404,28 +9551,28 @@
       <c r="B143" t="s">
         <v>18</v>
       </c>
-      <c r="C143" s="9">
-        <v>0</v>
-      </c>
-      <c r="D143" s="9">
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
         <v>0</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
       </c>
-      <c r="F143" s="9">
+      <c r="F143">
         <v>17</v>
       </c>
-      <c r="G143" s="9">
+      <c r="G143">
         <v>0.98086124401913799</v>
       </c>
-      <c r="H143" s="9">
+      <c r="H143">
         <v>44464690</v>
       </c>
       <c r="I143" t="s">
         <v>20</v>
       </c>
-      <c r="J143" s="9">
+      <c r="J143">
         <v>1332325685</v>
       </c>
       <c r="K143" t="s">
@@ -9457,28 +9604,28 @@
       <c r="B144" t="s">
         <v>18</v>
       </c>
-      <c r="C144" s="9">
-        <v>0</v>
-      </c>
-      <c r="D144" s="9">
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
         <v>0</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
       </c>
-      <c r="F144" s="9">
+      <c r="F144">
         <v>17</v>
       </c>
-      <c r="G144" s="9">
+      <c r="G144">
         <v>0.97619047619047605</v>
       </c>
-      <c r="H144" s="9">
+      <c r="H144">
         <v>44464690</v>
       </c>
       <c r="I144" t="s">
         <v>20</v>
       </c>
-      <c r="J144" s="9">
+      <c r="J144">
         <v>1332325685</v>
       </c>
       <c r="K144" t="s">
@@ -9510,28 +9657,28 @@
       <c r="B145" t="s">
         <v>18</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C145">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145">
         <v>2</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
       </c>
-      <c r="F145" s="9">
+      <c r="F145">
         <v>2</v>
       </c>
-      <c r="G145" s="9">
+      <c r="G145">
         <v>0.26595744680851002</v>
       </c>
-      <c r="H145" s="9">
+      <c r="H145">
         <v>44986521</v>
       </c>
       <c r="I145" t="s">
         <v>20</v>
       </c>
-      <c r="J145" s="9">
+      <c r="J145">
         <v>0</v>
       </c>
       <c r="K145" t="s">
@@ -9563,28 +9710,28 @@
       <c r="B146" t="s">
         <v>18</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146">
         <v>2</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
       </c>
-      <c r="F146" s="9">
+      <c r="F146">
         <v>2</v>
       </c>
-      <c r="G146" s="9">
+      <c r="G146">
         <v>0.26455026455026398</v>
       </c>
-      <c r="H146" s="9">
+      <c r="H146">
         <v>44986521</v>
       </c>
       <c r="I146" t="s">
         <v>20</v>
       </c>
-      <c r="J146" s="9">
+      <c r="J146">
         <v>0</v>
       </c>
       <c r="K146" t="s">
@@ -9616,28 +9763,28 @@
       <c r="B147" t="s">
         <v>18</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C147">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D147">
         <v>2</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
       </c>
-      <c r="F147" s="9">
+      <c r="F147">
         <v>2</v>
       </c>
-      <c r="G147" s="9">
+      <c r="G147">
         <v>0.26315789473684198</v>
       </c>
-      <c r="H147" s="9">
+      <c r="H147">
         <v>44986521</v>
       </c>
       <c r="I147" t="s">
         <v>20</v>
       </c>
-      <c r="J147" s="9">
+      <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
@@ -9669,28 +9816,28 @@
       <c r="B148" t="s">
         <v>18</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148">
         <v>1.19760479041916E-2</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148">
         <v>2</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
       </c>
-      <c r="F148" s="9">
+      <c r="F148">
         <v>2</v>
       </c>
-      <c r="G148" s="9">
+      <c r="G148">
         <v>0.261780104712041</v>
       </c>
-      <c r="H148" s="9">
+      <c r="H148">
         <v>44986521</v>
       </c>
       <c r="I148" t="s">
         <v>20</v>
       </c>
-      <c r="J148" s="9">
+      <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
@@ -9722,28 +9869,28 @@
       <c r="B149" t="s">
         <v>18</v>
       </c>
-      <c r="C149" s="9">
-        <v>0</v>
-      </c>
-      <c r="D149" s="9">
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
         <v>0</v>
       </c>
       <c r="E149" t="s">
         <v>19</v>
       </c>
-      <c r="F149" s="9">
+      <c r="F149">
         <v>16</v>
       </c>
-      <c r="G149" s="9">
+      <c r="G149">
         <v>1.0494505494505399</v>
       </c>
-      <c r="H149" s="9">
+      <c r="H149">
         <v>44464690</v>
       </c>
       <c r="I149" t="s">
         <v>20</v>
       </c>
-      <c r="J149" s="9">
+      <c r="J149">
         <v>1332325685</v>
       </c>
       <c r="K149" t="s">
@@ -9775,28 +9922,28 @@
       <c r="B150" t="s">
         <v>18</v>
       </c>
-      <c r="C150" s="9">
-        <v>0</v>
-      </c>
-      <c r="D150" s="9">
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
         <v>0</v>
       </c>
       <c r="E150" t="s">
         <v>19</v>
       </c>
-      <c r="F150" s="9">
+      <c r="F150">
         <v>16</v>
       </c>
-      <c r="G150" s="9">
+      <c r="G150">
         <v>1.04371584699453</v>
       </c>
-      <c r="H150" s="9">
+      <c r="H150">
         <v>44464690</v>
       </c>
       <c r="I150" t="s">
         <v>20</v>
       </c>
-      <c r="J150" s="9">
+      <c r="J150">
         <v>1332325685</v>
       </c>
       <c r="K150" t="s">
@@ -9828,28 +9975,28 @@
       <c r="B151" t="s">
         <v>18</v>
       </c>
-      <c r="C151" s="9">
-        <v>0</v>
-      </c>
-      <c r="D151" s="9">
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
         <v>0</v>
       </c>
       <c r="E151" t="s">
         <v>19</v>
       </c>
-      <c r="F151" s="9">
+      <c r="F151">
         <v>16</v>
       </c>
-      <c r="G151" s="9">
+      <c r="G151">
         <v>1.0380434782608601</v>
       </c>
-      <c r="H151" s="9">
+      <c r="H151">
         <v>44464690</v>
       </c>
       <c r="I151" t="s">
         <v>20</v>
       </c>
-      <c r="J151" s="9">
+      <c r="J151">
         <v>1332325685</v>
       </c>
       <c r="K151" t="s">
@@ -9881,28 +10028,28 @@
       <c r="B152" t="s">
         <v>18</v>
       </c>
-      <c r="C152" s="9">
-        <v>0</v>
-      </c>
-      <c r="D152" s="9">
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
         <v>0</v>
       </c>
       <c r="E152" t="s">
         <v>19</v>
       </c>
-      <c r="F152" s="9">
+      <c r="F152">
         <v>16</v>
       </c>
-      <c r="G152" s="9">
+      <c r="G152">
         <v>1.0324324324324301</v>
       </c>
-      <c r="H152" s="9">
+      <c r="H152">
         <v>44464690</v>
       </c>
       <c r="I152" t="s">
         <v>20</v>
       </c>
-      <c r="J152" s="9">
+      <c r="J152">
         <v>1332325685</v>
       </c>
       <c r="K152" t="s">
@@ -9934,28 +10081,28 @@
       <c r="B153" t="s">
         <v>18</v>
       </c>
-      <c r="C153" s="9">
-        <v>0</v>
-      </c>
-      <c r="D153" s="9">
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
         <v>0</v>
       </c>
       <c r="E153" t="s">
         <v>19</v>
       </c>
-      <c r="F153" s="9">
+      <c r="F153">
         <v>16</v>
       </c>
-      <c r="G153" s="9">
+      <c r="G153">
         <v>1.0268817204301</v>
       </c>
-      <c r="H153" s="9">
+      <c r="H153">
         <v>44464690</v>
       </c>
       <c r="I153" t="s">
         <v>20</v>
       </c>
-      <c r="J153" s="9">
+      <c r="J153">
         <v>1332325685</v>
       </c>
       <c r="K153" t="s">
@@ -9987,28 +10134,28 @@
       <c r="B154" t="s">
         <v>18</v>
       </c>
-      <c r="C154" s="9">
-        <v>0</v>
-      </c>
-      <c r="D154" s="9">
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
         <v>0</v>
       </c>
       <c r="E154" t="s">
         <v>19</v>
       </c>
-      <c r="F154" s="9">
+      <c r="F154">
         <v>16</v>
       </c>
-      <c r="G154" s="9">
+      <c r="G154">
         <v>1.02139037433155</v>
       </c>
-      <c r="H154" s="9">
+      <c r="H154">
         <v>44464690</v>
       </c>
       <c r="I154" t="s">
         <v>20</v>
       </c>
-      <c r="J154" s="9">
+      <c r="J154">
         <v>1332325685</v>
       </c>
       <c r="K154" t="s">
@@ -10040,28 +10187,28 @@
       <c r="B155" t="s">
         <v>18</v>
       </c>
-      <c r="C155" s="9">
-        <v>0</v>
-      </c>
-      <c r="D155" s="9">
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
         <v>0</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
       </c>
-      <c r="F155" s="9">
+      <c r="F155">
         <v>16</v>
       </c>
-      <c r="G155" s="9">
+      <c r="G155">
         <v>1.01595744680851</v>
       </c>
-      <c r="H155" s="9">
+      <c r="H155">
         <v>44464690</v>
       </c>
       <c r="I155" t="s">
         <v>20</v>
       </c>
-      <c r="J155" s="9">
+      <c r="J155">
         <v>1332325685</v>
       </c>
       <c r="K155" t="s">
@@ -10093,28 +10240,28 @@
       <c r="B156" t="s">
         <v>18</v>
       </c>
-      <c r="C156" s="9">
-        <v>0</v>
-      </c>
-      <c r="D156" s="9">
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
         <v>0</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
       </c>
-      <c r="F156" s="9">
+      <c r="F156">
         <v>16</v>
       </c>
-      <c r="G156" s="9">
+      <c r="G156">
         <v>1.01058201058201</v>
       </c>
-      <c r="H156" s="9">
+      <c r="H156">
         <v>44464690</v>
       </c>
       <c r="I156" t="s">
         <v>20</v>
       </c>
-      <c r="J156" s="9">
+      <c r="J156">
         <v>1332325685</v>
       </c>
       <c r="K156" t="s">
@@ -10146,28 +10293,28 @@
       <c r="B157" t="s">
         <v>18</v>
       </c>
-      <c r="C157" s="9">
+      <c r="C157">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D157" s="9">
+      <c r="D157">
         <v>1</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
       </c>
-      <c r="F157" s="9">
-        <v>1</v>
-      </c>
-      <c r="G157" s="9">
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157">
         <v>0.101694915254237</v>
       </c>
-      <c r="H157" s="9">
+      <c r="H157">
         <v>44986521</v>
       </c>
       <c r="I157" t="s">
         <v>20</v>
       </c>
-      <c r="J157" s="9">
+      <c r="J157">
         <v>0</v>
       </c>
       <c r="K157" t="s">
@@ -10199,28 +10346,28 @@
       <c r="B158" t="s">
         <v>18</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D158" s="9">
+      <c r="D158">
         <v>1</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
       </c>
-      <c r="F158" s="9">
-        <v>1</v>
-      </c>
-      <c r="G158" s="9">
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
         <v>9.8360655737704902E-2</v>
       </c>
-      <c r="H158" s="9">
+      <c r="H158">
         <v>44986521</v>
       </c>
       <c r="I158" t="s">
         <v>20</v>
       </c>
-      <c r="J158" s="9">
+      <c r="J158">
         <v>0</v>
       </c>
       <c r="K158" t="s">
@@ -10252,28 +10399,28 @@
       <c r="B159" t="s">
         <v>18</v>
       </c>
-      <c r="C159" s="9">
+      <c r="C159">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D159" s="9">
+      <c r="D159">
         <v>1</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
       </c>
-      <c r="F159" s="9">
-        <v>1</v>
-      </c>
-      <c r="G159" s="9">
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
         <v>9.7560975609756101E-2</v>
       </c>
-      <c r="H159" s="9">
+      <c r="H159">
         <v>44986521</v>
       </c>
       <c r="I159" t="s">
         <v>20</v>
       </c>
-      <c r="J159" s="9">
+      <c r="J159">
         <v>0</v>
       </c>
       <c r="K159" t="s">
@@ -10305,28 +10452,28 @@
       <c r="B160" t="s">
         <v>18</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160">
         <v>1</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
       </c>
-      <c r="F160" s="9">
-        <v>1</v>
-      </c>
-      <c r="G160" s="9">
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="H160" s="9">
+      <c r="H160">
         <v>44986521</v>
       </c>
       <c r="I160" t="s">
         <v>20</v>
       </c>
-      <c r="J160" s="9">
+      <c r="J160">
         <v>0</v>
       </c>
       <c r="K160" t="s">
@@ -10358,28 +10505,28 @@
       <c r="B161" t="s">
         <v>18</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C161">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D161" s="9">
+      <c r="D161">
         <v>1</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
       </c>
-      <c r="F161" s="9">
-        <v>1</v>
-      </c>
-      <c r="G161" s="9">
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="H161" s="9">
+      <c r="H161">
         <v>44986521</v>
       </c>
       <c r="I161" t="s">
         <v>20</v>
       </c>
-      <c r="J161" s="9">
+      <c r="J161">
         <v>0</v>
       </c>
       <c r="K161" t="s">
@@ -10411,28 +10558,28 @@
       <c r="B162" t="s">
         <v>18</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D162" s="9">
+      <c r="D162">
         <v>1</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
       </c>
-      <c r="F162" s="9">
-        <v>1</v>
-      </c>
-      <c r="G162" s="9">
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="G162">
         <v>9.5238095238095205E-2</v>
       </c>
-      <c r="H162" s="9">
+      <c r="H162">
         <v>44986521</v>
       </c>
       <c r="I162" t="s">
         <v>20</v>
       </c>
-      <c r="J162" s="9">
+      <c r="J162">
         <v>0</v>
       </c>
       <c r="K162" t="s">
@@ -10464,28 +10611,28 @@
       <c r="B163" t="s">
         <v>18</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C163">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D163" s="9">
+      <c r="D163">
         <v>1</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
       </c>
-      <c r="F163" s="9">
-        <v>1</v>
-      </c>
-      <c r="G163" s="9">
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
         <v>9.4488188976377896E-2</v>
       </c>
-      <c r="H163" s="9">
+      <c r="H163">
         <v>44986521</v>
       </c>
       <c r="I163" t="s">
         <v>20</v>
       </c>
-      <c r="J163" s="9">
+      <c r="J163">
         <v>0</v>
       </c>
       <c r="K163" t="s">
@@ -10517,28 +10664,28 @@
       <c r="B164" t="s">
         <v>18</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D164" s="9">
+      <c r="D164">
         <v>1</v>
       </c>
       <c r="E164" t="s">
         <v>19</v>
       </c>
-      <c r="F164" s="9">
-        <v>1</v>
-      </c>
-      <c r="G164" s="9">
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="G164">
         <v>9.375E-2</v>
       </c>
-      <c r="H164" s="9">
+      <c r="H164">
         <v>44986521</v>
       </c>
       <c r="I164" t="s">
         <v>20</v>
       </c>
-      <c r="J164" s="9">
+      <c r="J164">
         <v>0</v>
       </c>
       <c r="K164" t="s">
@@ -10570,28 +10717,28 @@
       <c r="B165" t="s">
         <v>18</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C165">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D165" s="9">
+      <c r="D165">
         <v>1</v>
       </c>
       <c r="E165" t="s">
         <v>19</v>
       </c>
-      <c r="F165" s="9">
-        <v>1</v>
-      </c>
-      <c r="G165" s="9">
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="G165">
         <v>9.3023255813953404E-2</v>
       </c>
-      <c r="H165" s="9">
+      <c r="H165">
         <v>44986521</v>
       </c>
       <c r="I165" t="s">
         <v>20</v>
       </c>
-      <c r="J165" s="9">
+      <c r="J165">
         <v>0</v>
       </c>
       <c r="K165" t="s">
@@ -10623,28 +10770,28 @@
       <c r="B166" t="s">
         <v>18</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166">
         <v>1</v>
       </c>
       <c r="E166" t="s">
         <v>19</v>
       </c>
-      <c r="F166" s="9">
-        <v>1</v>
-      </c>
-      <c r="G166" s="9">
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166">
         <v>9.2307692307692299E-2</v>
       </c>
-      <c r="H166" s="9">
+      <c r="H166">
         <v>44986521</v>
       </c>
       <c r="I166" t="s">
         <v>20</v>
       </c>
-      <c r="J166" s="9">
+      <c r="J166">
         <v>0</v>
       </c>
       <c r="K166" t="s">
@@ -10676,28 +10823,28 @@
       <c r="B167" t="s">
         <v>18</v>
       </c>
-      <c r="C167" s="9">
+      <c r="C167">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D167" s="9">
+      <c r="D167">
         <v>1</v>
       </c>
       <c r="E167" t="s">
         <v>19</v>
       </c>
-      <c r="F167" s="9">
-        <v>1</v>
-      </c>
-      <c r="G167" s="9">
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
         <v>9.1603053435114504E-2</v>
       </c>
-      <c r="H167" s="9">
+      <c r="H167">
         <v>44986521</v>
       </c>
       <c r="I167" t="s">
         <v>20</v>
       </c>
-      <c r="J167" s="9">
+      <c r="J167">
         <v>0</v>
       </c>
       <c r="K167" t="s">
@@ -10729,28 +10876,28 @@
       <c r="B168" t="s">
         <v>18</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D168" s="9">
+      <c r="D168">
         <v>1</v>
       </c>
       <c r="E168" t="s">
         <v>19</v>
       </c>
-      <c r="F168" s="9">
-        <v>1</v>
-      </c>
-      <c r="G168" s="9">
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
         <v>9.0909090909090898E-2</v>
       </c>
-      <c r="H168" s="9">
+      <c r="H168">
         <v>44986521</v>
       </c>
       <c r="I168" t="s">
         <v>20</v>
       </c>
-      <c r="J168" s="9">
+      <c r="J168">
         <v>0</v>
       </c>
       <c r="K168" t="s">
@@ -10782,28 +10929,28 @@
       <c r="B169" t="s">
         <v>18</v>
       </c>
-      <c r="C169" s="9">
+      <c r="C169">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D169" s="9">
+      <c r="D169">
         <v>1</v>
       </c>
       <c r="E169" t="s">
         <v>19</v>
       </c>
-      <c r="F169" s="9">
-        <v>1</v>
-      </c>
-      <c r="G169" s="9">
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169">
         <v>9.0225563909774403E-2</v>
       </c>
-      <c r="H169" s="9">
+      <c r="H169">
         <v>44986521</v>
       </c>
       <c r="I169" t="s">
         <v>20</v>
       </c>
-      <c r="J169" s="9">
+      <c r="J169">
         <v>0</v>
       </c>
       <c r="K169" t="s">
@@ -10835,28 +10982,28 @@
       <c r="B170" t="s">
         <v>18</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D170" s="9">
+      <c r="D170">
         <v>1</v>
       </c>
       <c r="E170" t="s">
         <v>19</v>
       </c>
-      <c r="F170" s="9">
-        <v>1</v>
-      </c>
-      <c r="G170" s="9">
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
         <v>8.9552238805970102E-2</v>
       </c>
-      <c r="H170" s="9">
+      <c r="H170">
         <v>44986521</v>
       </c>
       <c r="I170" t="s">
         <v>20</v>
       </c>
-      <c r="J170" s="9">
+      <c r="J170">
         <v>0</v>
       </c>
       <c r="K170" t="s">
@@ -10888,28 +11035,28 @@
       <c r="B171" t="s">
         <v>18</v>
       </c>
-      <c r="C171" s="9">
+      <c r="C171">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D171" s="9">
+      <c r="D171">
         <v>1</v>
       </c>
       <c r="E171" t="s">
         <v>19</v>
       </c>
-      <c r="F171" s="9">
-        <v>1</v>
-      </c>
-      <c r="G171" s="9">
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171">
         <v>8.8888888888888795E-2</v>
       </c>
-      <c r="H171" s="9">
+      <c r="H171">
         <v>44986521</v>
       </c>
       <c r="I171" t="s">
         <v>20</v>
       </c>
-      <c r="J171" s="9">
+      <c r="J171">
         <v>0</v>
       </c>
       <c r="K171" t="s">
@@ -10941,28 +11088,28 @@
       <c r="B172" t="s">
         <v>18</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D172" s="9">
+      <c r="D172">
         <v>1</v>
       </c>
       <c r="E172" t="s">
         <v>19</v>
       </c>
-      <c r="F172" s="9">
-        <v>1</v>
-      </c>
-      <c r="G172" s="9">
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
         <v>8.8235294117646995E-2</v>
       </c>
-      <c r="H172" s="9">
+      <c r="H172">
         <v>44986521</v>
       </c>
       <c r="I172" t="s">
         <v>20</v>
       </c>
-      <c r="J172" s="9">
+      <c r="J172">
         <v>0</v>
       </c>
       <c r="K172" t="s">
@@ -10994,28 +11141,28 @@
       <c r="B173" t="s">
         <v>18</v>
       </c>
-      <c r="C173" s="9">
+      <c r="C173">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D173" s="9">
+      <c r="D173">
         <v>1</v>
       </c>
       <c r="E173" t="s">
         <v>19</v>
       </c>
-      <c r="F173" s="9">
-        <v>1</v>
-      </c>
-      <c r="G173" s="9">
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173">
         <v>8.7591240875912399E-2</v>
       </c>
-      <c r="H173" s="9">
+      <c r="H173">
         <v>44986521</v>
       </c>
       <c r="I173" t="s">
         <v>20</v>
       </c>
-      <c r="J173" s="9">
+      <c r="J173">
         <v>0</v>
       </c>
       <c r="K173" t="s">
@@ -11047,28 +11194,28 @@
       <c r="B174" t="s">
         <v>18</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D174" s="9">
+      <c r="D174">
         <v>1</v>
       </c>
       <c r="E174" t="s">
         <v>19</v>
       </c>
-      <c r="F174" s="9">
-        <v>1</v>
-      </c>
-      <c r="G174" s="9">
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174">
         <v>8.6956521739130405E-2</v>
       </c>
-      <c r="H174" s="9">
+      <c r="H174">
         <v>44986521</v>
       </c>
       <c r="I174" t="s">
         <v>20</v>
       </c>
-      <c r="J174" s="9">
+      <c r="J174">
         <v>0</v>
       </c>
       <c r="K174" t="s">
@@ -11100,28 +11247,28 @@
       <c r="B175" t="s">
         <v>18</v>
       </c>
-      <c r="C175" s="9">
+      <c r="C175">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D175" s="9">
+      <c r="D175">
         <v>1</v>
       </c>
       <c r="E175" t="s">
         <v>19</v>
       </c>
-      <c r="F175" s="9">
-        <v>1</v>
-      </c>
-      <c r="G175" s="9">
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175">
         <v>8.6330935251798496E-2</v>
       </c>
-      <c r="H175" s="9">
+      <c r="H175">
         <v>44986521</v>
       </c>
       <c r="I175" t="s">
         <v>20</v>
       </c>
-      <c r="J175" s="9">
+      <c r="J175">
         <v>0</v>
       </c>
       <c r="K175" t="s">
@@ -11153,28 +11300,28 @@
       <c r="B176" t="s">
         <v>18</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D176" s="9">
+      <c r="D176">
         <v>1</v>
       </c>
       <c r="E176" t="s">
         <v>19</v>
       </c>
-      <c r="F176" s="9">
-        <v>1</v>
-      </c>
-      <c r="G176" s="9">
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176">
         <v>8.5714285714285701E-2</v>
       </c>
-      <c r="H176" s="9">
+      <c r="H176">
         <v>44986521</v>
       </c>
       <c r="I176" t="s">
         <v>20</v>
       </c>
-      <c r="J176" s="9">
+      <c r="J176">
         <v>0</v>
       </c>
       <c r="K176" t="s">
@@ -11206,28 +11353,28 @@
       <c r="B177" t="s">
         <v>18</v>
       </c>
-      <c r="C177" s="9">
+      <c r="C177">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D177" s="9">
+      <c r="D177">
         <v>1</v>
       </c>
       <c r="E177" t="s">
         <v>19</v>
       </c>
-      <c r="F177" s="9">
-        <v>1</v>
-      </c>
-      <c r="G177" s="9">
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177">
         <v>8.5106382978723402E-2</v>
       </c>
-      <c r="H177" s="9">
+      <c r="H177">
         <v>44986521</v>
       </c>
       <c r="I177" t="s">
         <v>20</v>
       </c>
-      <c r="J177" s="9">
+      <c r="J177">
         <v>0</v>
       </c>
       <c r="K177" t="s">
@@ -11259,28 +11406,28 @@
       <c r="B178" t="s">
         <v>18</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C178">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D178" s="9">
+      <c r="D178">
         <v>1</v>
       </c>
       <c r="E178" t="s">
         <v>19</v>
       </c>
-      <c r="F178" s="9">
-        <v>1</v>
-      </c>
-      <c r="G178" s="9">
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
         <v>0.08</v>
       </c>
-      <c r="H178" s="9">
+      <c r="H178">
         <v>44986521</v>
       </c>
       <c r="I178" t="s">
         <v>20</v>
       </c>
-      <c r="J178" s="9">
+      <c r="J178">
         <v>0</v>
       </c>
       <c r="K178" t="s">
@@ -11312,28 +11459,28 @@
       <c r="B179" t="s">
         <v>18</v>
       </c>
-      <c r="C179" s="9">
+      <c r="C179">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D179" s="9">
+      <c r="D179">
         <v>1</v>
       </c>
       <c r="E179" t="s">
         <v>19</v>
       </c>
-      <c r="F179" s="9">
-        <v>1</v>
-      </c>
-      <c r="G179" s="9">
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
         <v>7.9470198675496595E-2</v>
       </c>
-      <c r="H179" s="9">
+      <c r="H179">
         <v>44986521</v>
       </c>
       <c r="I179" t="s">
         <v>20</v>
       </c>
-      <c r="J179" s="9">
+      <c r="J179">
         <v>0</v>
       </c>
       <c r="K179" t="s">
@@ -11365,28 +11512,28 @@
       <c r="B180" t="s">
         <v>18</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C180">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D180" s="9">
+      <c r="D180">
         <v>1</v>
       </c>
       <c r="E180" t="s">
         <v>19</v>
       </c>
-      <c r="F180" s="9">
-        <v>1</v>
-      </c>
-      <c r="G180" s="9">
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
         <v>7.8947368421052599E-2</v>
       </c>
-      <c r="H180" s="9">
+      <c r="H180">
         <v>44986521</v>
       </c>
       <c r="I180" t="s">
         <v>20</v>
       </c>
-      <c r="J180" s="9">
+      <c r="J180">
         <v>0</v>
       </c>
       <c r="K180" t="s">
@@ -11418,28 +11565,28 @@
       <c r="B181" t="s">
         <v>18</v>
       </c>
-      <c r="C181" s="9">
+      <c r="C181">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D181" s="9">
+      <c r="D181">
         <v>1</v>
       </c>
       <c r="E181" t="s">
         <v>19</v>
       </c>
-      <c r="F181" s="9">
-        <v>1</v>
-      </c>
-      <c r="G181" s="9">
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
         <v>7.8431372549019607E-2</v>
       </c>
-      <c r="H181" s="9">
+      <c r="H181">
         <v>44986521</v>
       </c>
       <c r="I181" t="s">
         <v>20</v>
       </c>
-      <c r="J181" s="9">
+      <c r="J181">
         <v>0</v>
       </c>
       <c r="K181" t="s">
@@ -11471,28 +11618,28 @@
       <c r="B182" t="s">
         <v>18</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C182">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D182" s="9">
+      <c r="D182">
         <v>1</v>
       </c>
       <c r="E182" t="s">
         <v>19</v>
       </c>
-      <c r="F182" s="9">
-        <v>1</v>
-      </c>
-      <c r="G182" s="9">
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
         <v>7.7922077922077906E-2</v>
       </c>
-      <c r="H182" s="9">
+      <c r="H182">
         <v>44986521</v>
       </c>
       <c r="I182" t="s">
         <v>20</v>
       </c>
-      <c r="J182" s="9">
+      <c r="J182">
         <v>0</v>
       </c>
       <c r="K182" t="s">
@@ -11524,28 +11671,28 @@
       <c r="B183" t="s">
         <v>18</v>
       </c>
-      <c r="C183" s="9">
+      <c r="C183">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D183" s="9">
+      <c r="D183">
         <v>1</v>
       </c>
       <c r="E183" t="s">
         <v>19</v>
       </c>
-      <c r="F183" s="9">
-        <v>1</v>
-      </c>
-      <c r="G183" s="9">
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
         <v>7.7419354838709598E-2</v>
       </c>
-      <c r="H183" s="9">
+      <c r="H183">
         <v>44986521</v>
       </c>
       <c r="I183" t="s">
         <v>20</v>
       </c>
-      <c r="J183" s="9">
+      <c r="J183">
         <v>0</v>
       </c>
       <c r="K183" t="s">
@@ -11577,28 +11724,28 @@
       <c r="B184" t="s">
         <v>18</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C184">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D184" s="9">
+      <c r="D184">
         <v>1</v>
       </c>
       <c r="E184" t="s">
         <v>19</v>
       </c>
-      <c r="F184" s="9">
-        <v>1</v>
-      </c>
-      <c r="G184" s="9">
+      <c r="F184">
+        <v>1</v>
+      </c>
+      <c r="G184">
         <v>7.69230769230769E-2</v>
       </c>
-      <c r="H184" s="9">
+      <c r="H184">
         <v>44986521</v>
       </c>
       <c r="I184" t="s">
         <v>20</v>
       </c>
-      <c r="J184" s="9">
+      <c r="J184">
         <v>0</v>
       </c>
       <c r="K184" t="s">
@@ -11630,28 +11777,28 @@
       <c r="B185" t="s">
         <v>18</v>
       </c>
-      <c r="C185" s="9">
+      <c r="C185">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D185" s="9">
+      <c r="D185">
         <v>1</v>
       </c>
       <c r="E185" t="s">
         <v>19</v>
       </c>
-      <c r="F185" s="9">
-        <v>1</v>
-      </c>
-      <c r="G185" s="9">
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
         <v>7.6433121019108194E-2</v>
       </c>
-      <c r="H185" s="9">
+      <c r="H185">
         <v>44986521</v>
       </c>
       <c r="I185" t="s">
         <v>20</v>
       </c>
-      <c r="J185" s="9">
+      <c r="J185">
         <v>0</v>
       </c>
       <c r="K185" t="s">
@@ -11683,28 +11830,28 @@
       <c r="B186" t="s">
         <v>18</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C186">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D186" s="9">
+      <c r="D186">
         <v>1</v>
       </c>
       <c r="E186" t="s">
         <v>19</v>
       </c>
-      <c r="F186" s="9">
-        <v>1</v>
-      </c>
-      <c r="G186" s="9">
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186">
         <v>7.5949367088607597E-2</v>
       </c>
-      <c r="H186" s="9">
+      <c r="H186">
         <v>44986521</v>
       </c>
       <c r="I186" t="s">
         <v>20</v>
       </c>
-      <c r="J186" s="9">
+      <c r="J186">
         <v>0</v>
       </c>
       <c r="K186" t="s">
@@ -11736,28 +11883,28 @@
       <c r="B187" t="s">
         <v>18</v>
       </c>
-      <c r="C187" s="9">
+      <c r="C187">
         <v>1.23456790123456E-2</v>
       </c>
-      <c r="D187" s="9">
+      <c r="D187">
         <v>1</v>
       </c>
       <c r="E187" t="s">
         <v>19</v>
       </c>
-      <c r="F187" s="9">
-        <v>1</v>
-      </c>
-      <c r="G187" s="9">
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
         <v>7.5471698113207503E-2</v>
       </c>
-      <c r="H187" s="9">
+      <c r="H187">
         <v>44986521</v>
       </c>
       <c r="I187" t="s">
         <v>20</v>
       </c>
-      <c r="J187" s="9">
+      <c r="J187">
         <v>0</v>
       </c>
       <c r="K187" t="s">
@@ -11789,28 +11936,28 @@
       <c r="B188" t="s">
         <v>18</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C188">
         <v>0.14527320034692101</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188">
         <v>335</v>
       </c>
       <c r="E188" t="s">
         <v>19</v>
       </c>
-      <c r="F188" s="9">
+      <c r="F188">
         <v>2345</v>
       </c>
-      <c r="G188" s="9">
+      <c r="G188">
         <v>1.03125</v>
       </c>
-      <c r="H188" s="9">
+      <c r="H188">
         <v>8200826</v>
       </c>
       <c r="I188" t="s">
         <v>20</v>
       </c>
-      <c r="J188" s="9">
+      <c r="J188">
         <v>922514082</v>
       </c>
       <c r="K188" t="s">
@@ -11842,28 +11989,28 @@
       <c r="B189" t="s">
         <v>18</v>
       </c>
-      <c r="C189" s="9">
-        <v>0</v>
-      </c>
-      <c r="D189" s="9">
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
         <v>0</v>
       </c>
       <c r="E189" t="s">
         <v>19</v>
       </c>
-      <c r="F189" s="9">
+      <c r="F189">
         <v>16</v>
       </c>
-      <c r="G189" s="9">
+      <c r="G189">
         <v>1.0674157303370699</v>
       </c>
-      <c r="H189" s="9">
+      <c r="H189">
         <v>44464690</v>
       </c>
       <c r="I189" t="s">
         <v>20</v>
       </c>
-      <c r="J189" s="9">
+      <c r="J189">
         <v>1332325685</v>
       </c>
       <c r="K189" t="s">
@@ -11895,28 +12042,28 @@
       <c r="B190" t="s">
         <v>18</v>
       </c>
-      <c r="C190" s="9">
-        <v>0</v>
-      </c>
-      <c r="D190" s="9">
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
         <v>0</v>
       </c>
       <c r="E190" t="s">
         <v>19</v>
       </c>
-      <c r="F190" s="9">
+      <c r="F190">
         <v>16</v>
       </c>
-      <c r="G190" s="9">
+      <c r="G190">
         <v>1.0614525139664801</v>
       </c>
-      <c r="H190" s="9">
+      <c r="H190">
         <v>44464690</v>
       </c>
       <c r="I190" t="s">
         <v>20</v>
       </c>
-      <c r="J190" s="9">
+      <c r="J190">
         <v>1332325685</v>
       </c>
       <c r="K190" t="s">
@@ -11948,28 +12095,28 @@
       <c r="B191" t="s">
         <v>18</v>
       </c>
-      <c r="C191" s="9">
-        <v>0</v>
-      </c>
-      <c r="D191" s="9">
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
         <v>0</v>
       </c>
       <c r="E191" t="s">
         <v>19</v>
       </c>
-      <c r="F191" s="9">
+      <c r="F191">
         <v>16</v>
       </c>
-      <c r="G191" s="9">
+      <c r="G191">
         <v>1.06111111111111</v>
       </c>
-      <c r="H191" s="9">
+      <c r="H191">
         <v>44464690</v>
       </c>
       <c r="I191" t="s">
         <v>20</v>
       </c>
-      <c r="J191" s="9">
+      <c r="J191">
         <v>1332325685</v>
       </c>
       <c r="K191" t="s">
@@ -12001,28 +12148,28 @@
       <c r="B192" t="s">
         <v>18</v>
       </c>
-      <c r="C192" s="9">
-        <v>0</v>
-      </c>
-      <c r="D192" s="9">
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
         <v>0</v>
       </c>
       <c r="E192" t="s">
         <v>19</v>
       </c>
-      <c r="F192" s="9">
+      <c r="F192">
         <v>16</v>
       </c>
-      <c r="G192" s="9">
+      <c r="G192">
         <v>1.05524861878453</v>
       </c>
-      <c r="H192" s="9">
+      <c r="H192">
         <v>44464690</v>
       </c>
       <c r="I192" t="s">
         <v>20</v>
       </c>
-      <c r="J192" s="9">
+      <c r="J192">
         <v>1332325685</v>
       </c>
       <c r="K192" t="s">
@@ -12054,28 +12201,28 @@
       <c r="B193" t="s">
         <v>18</v>
       </c>
-      <c r="C193" s="9">
+      <c r="C193">
         <v>0.32288401253918497</v>
       </c>
-      <c r="D193" s="9">
+      <c r="D193">
         <v>103</v>
       </c>
       <c r="E193" t="s">
         <v>19</v>
       </c>
-      <c r="F193" s="9">
+      <c r="F193">
         <v>396</v>
       </c>
-      <c r="G193" s="9">
-        <v>0</v>
-      </c>
-      <c r="H193" s="9">
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
         <v>34917006</v>
       </c>
       <c r="I193" t="s">
         <v>20</v>
       </c>
-      <c r="J193" s="9">
+      <c r="J193">
         <v>0</v>
       </c>
       <c r="K193" t="s">
@@ -12107,28 +12254,28 @@
       <c r="B194" t="s">
         <v>18</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C194">
         <v>0.32288401253918497</v>
       </c>
-      <c r="D194" s="9">
+      <c r="D194">
         <v>103</v>
       </c>
       <c r="E194" t="s">
         <v>19</v>
       </c>
-      <c r="F194" s="9">
+      <c r="F194">
         <v>396</v>
       </c>
-      <c r="G194" s="9">
-        <v>0</v>
-      </c>
-      <c r="H194" s="9">
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
         <v>34917006</v>
       </c>
       <c r="I194" t="s">
         <v>20</v>
       </c>
-      <c r="J194" s="9">
+      <c r="J194">
         <v>0</v>
       </c>
       <c r="K194" t="s">
@@ -12160,28 +12307,28 @@
       <c r="B195" t="s">
         <v>18</v>
       </c>
-      <c r="C195" s="9">
-        <v>0</v>
-      </c>
-      <c r="D195" s="9">
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
         <v>0</v>
       </c>
       <c r="E195" t="s">
         <v>19</v>
       </c>
-      <c r="F195" s="9">
+      <c r="F195">
         <v>5</v>
       </c>
-      <c r="G195" s="9">
+      <c r="G195">
         <v>0.90243902439024304</v>
       </c>
-      <c r="H195" s="9">
+      <c r="H195">
         <v>44795713</v>
       </c>
       <c r="I195" t="s">
         <v>20</v>
       </c>
-      <c r="J195" s="9">
+      <c r="J195">
         <v>0</v>
       </c>
       <c r="K195" t="s">
@@ -12213,28 +12360,28 @@
       <c r="B196" t="s">
         <v>18</v>
       </c>
-      <c r="C196" s="9">
-        <v>0</v>
-      </c>
-      <c r="D196" s="9">
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
         <v>0</v>
       </c>
       <c r="E196" t="s">
         <v>19</v>
       </c>
-      <c r="F196" s="9">
+      <c r="F196">
         <v>5</v>
       </c>
-      <c r="G196" s="9">
+      <c r="G196">
         <v>0.86046511627906896</v>
       </c>
-      <c r="H196" s="9">
+      <c r="H196">
         <v>44795713</v>
       </c>
       <c r="I196" t="s">
         <v>20</v>
       </c>
-      <c r="J196" s="9">
+      <c r="J196">
         <v>0</v>
       </c>
       <c r="K196" t="s">
@@ -12266,28 +12413,28 @@
       <c r="B197" t="s">
         <v>18</v>
       </c>
-      <c r="C197" s="9">
-        <v>0</v>
-      </c>
-      <c r="D197" s="9">
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
         <v>0</v>
       </c>
       <c r="E197" t="s">
         <v>19</v>
       </c>
-      <c r="F197" s="9">
+      <c r="F197">
         <v>249</v>
       </c>
-      <c r="G197" s="9">
+      <c r="G197">
         <v>0.88888888888888795</v>
       </c>
-      <c r="H197" s="9">
+      <c r="H197">
         <v>38375955</v>
       </c>
       <c r="I197" t="s">
         <v>20</v>
       </c>
-      <c r="J197" s="9">
+      <c r="J197">
         <v>0</v>
       </c>
       <c r="K197" t="s">
@@ -12319,28 +12466,28 @@
       <c r="B198" t="s">
         <v>18</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C198">
         <v>0.14677700348431999</v>
       </c>
-      <c r="D198" s="9">
+      <c r="D198">
         <v>337</v>
       </c>
       <c r="E198" t="s">
         <v>19</v>
       </c>
-      <c r="F198" s="9">
+      <c r="F198">
         <v>2343</v>
       </c>
-      <c r="G198" s="9">
+      <c r="G198">
         <v>0.78846153846153799</v>
       </c>
-      <c r="H198" s="9">
+      <c r="H198">
         <v>8200826</v>
       </c>
       <c r="I198" t="s">
         <v>20</v>
       </c>
-      <c r="J198" s="9">
+      <c r="J198">
         <v>922514082</v>
       </c>
       <c r="K198" t="s">
@@ -12372,28 +12519,28 @@
       <c r="B199" t="s">
         <v>18</v>
       </c>
-      <c r="C199" s="9">
-        <v>0</v>
-      </c>
-      <c r="D199" s="9">
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
         <v>0</v>
       </c>
       <c r="E199" t="s">
         <v>19</v>
       </c>
-      <c r="F199" s="9">
+      <c r="F199">
         <v>16</v>
       </c>
-      <c r="G199" s="9">
+      <c r="G199">
         <v>0.94059405940593999</v>
       </c>
-      <c r="H199" s="9">
+      <c r="H199">
         <v>44464690</v>
       </c>
       <c r="I199" t="s">
         <v>20</v>
       </c>
-      <c r="J199" s="9">
+      <c r="J199">
         <v>1332325685</v>
       </c>
       <c r="K199" t="s">
@@ -12425,28 +12572,28 @@
       <c r="B200" t="s">
         <v>18</v>
       </c>
-      <c r="C200" s="9">
-        <v>0</v>
-      </c>
-      <c r="D200" s="9">
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
         <v>0</v>
       </c>
       <c r="E200" t="s">
         <v>19</v>
       </c>
-      <c r="F200" s="9">
+      <c r="F200">
         <v>16</v>
       </c>
-      <c r="G200" s="9">
+      <c r="G200">
         <v>0.93596059113300401</v>
       </c>
-      <c r="H200" s="9">
+      <c r="H200">
         <v>44464690</v>
       </c>
       <c r="I200" t="s">
         <v>20</v>
       </c>
-      <c r="J200" s="9">
+      <c r="J200">
         <v>1332325685</v>
       </c>
       <c r="K200" t="s">
@@ -12478,28 +12625,28 @@
       <c r="B201" t="s">
         <v>18</v>
       </c>
-      <c r="C201" s="9">
-        <v>0</v>
-      </c>
-      <c r="D201" s="9">
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
         <v>0</v>
       </c>
       <c r="E201" t="s">
         <v>19</v>
       </c>
-      <c r="F201" s="9">
+      <c r="F201">
         <v>16</v>
       </c>
-      <c r="G201" s="9">
+      <c r="G201">
         <v>0.93137254901960698</v>
       </c>
-      <c r="H201" s="9">
+      <c r="H201">
         <v>44464690</v>
       </c>
       <c r="I201" t="s">
         <v>20</v>
       </c>
-      <c r="J201" s="9">
+      <c r="J201">
         <v>1332325685</v>
       </c>
       <c r="K201" t="s">
@@ -12531,28 +12678,28 @@
       <c r="B202" t="s">
         <v>18</v>
       </c>
-      <c r="C202" s="9">
+      <c r="C202">
         <v>0.14513350559862101</v>
       </c>
-      <c r="D202" s="9">
+      <c r="D202">
         <v>337</v>
       </c>
       <c r="E202" t="s">
         <v>19</v>
       </c>
-      <c r="F202" s="9">
+      <c r="F202">
         <v>2347</v>
       </c>
-      <c r="G202" s="9">
+      <c r="G202">
         <v>0.63636363636363602</v>
       </c>
-      <c r="H202" s="9">
+      <c r="H202">
         <v>8200826</v>
       </c>
       <c r="I202" t="s">
         <v>20</v>
       </c>
-      <c r="J202" s="9">
+      <c r="J202">
         <v>922514082</v>
       </c>
       <c r="K202" t="s">
@@ -12578,6 +12725,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q202" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -13609,23 +13757,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5EC4E4-D55E-442C-807A-E9BE0ADB2D6F}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>368</v>
       </c>
@@ -13656,12 +13807,734 @@
       <c r="J1" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>378</v>
       </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="str">
+        <f>HYPERLINK("https://sg-athena.lalamove.work/users/"&amp;B2&amp;"/overview?city_id=100000","User Athena")</f>
+        <v>User Athena</v>
+      </c>
+      <c r="B2">
+        <v>8200826</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B2)</f>
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2">
+        <f ca="1">ROUNDUP(TODAY()-C2,0)</f>
+        <v>2352</v>
+      </c>
+      <c r="J2" s="10">
+        <v>0.19567262464722485</v>
+      </c>
+      <c r="K2" t="s">
+        <v>380</v>
+      </c>
+      <c r="N2" t="s">
+        <v>379</v>
+      </c>
+      <c r="O2">
+        <f>COUNTIF($K$2:$K$16,N2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="str">
+        <f t="shared" ref="A3:A16" si="0">HYPERLINK("https://sg-athena.lalamove.work/users/"&amp;B3&amp;"/overview?city_id=100000","User Athena")</f>
+        <v>User Athena</v>
+      </c>
+      <c r="B3">
+        <v>44465314</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F3">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I16" ca="1" si="1">ROUNDUP(TODAY()-C3,0)</f>
+        <v>24</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L3" t="s">
+        <v>381</v>
+      </c>
+      <c r="N3" t="s">
+        <v>380</v>
+      </c>
+      <c r="O3">
+        <f>COUNTIF($K$2:$K$16,N3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B4">
+        <v>45055754</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B4)</f>
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J4" s="10">
+        <v>2.9411764705882353E-2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B5">
+        <v>45042918</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B5)</f>
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46301.466782407406</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>379</v>
+      </c>
+      <c r="N5" t="s">
+        <v>382</v>
+      </c>
+      <c r="O5" s="10">
+        <f>O2/(O2+O3)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B6">
+        <v>44986521</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F6">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B6)</f>
+        <v>93</v>
+      </c>
+      <c r="G6" t="s">
+        <v>303</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I6">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J6" s="10">
+        <v>1.0050251256281407E-2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B7">
+        <v>44464690</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F7">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B7)</f>
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>309</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I7">
+        <f t="shared" ca="1" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B8">
+        <v>44795713</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B8)</f>
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>314</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ca="1" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B9">
+        <v>28625427</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>283</v>
+      </c>
+      <c r="E9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F9">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B9)</f>
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9">
+        <f t="shared" ca="1" si="1"/>
+        <v>697</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0.25950413223140495</v>
+      </c>
+      <c r="K9" t="s">
+        <v>380</v>
+      </c>
+      <c r="N9" t="s">
+        <v>385</v>
+      </c>
+      <c r="O9" s="11">
+        <v>2.5336541115912031E-3</v>
+      </c>
+      <c r="P9" s="11"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B10">
+        <v>44643928</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F10">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B10)</f>
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ca="1" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="J10" s="10">
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>379</v>
+      </c>
+      <c r="N10" t="s">
+        <v>386</v>
+      </c>
+      <c r="O10" s="11">
+        <v>6.4233941728680972E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B11">
+        <v>44003760</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F11">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B11)</f>
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11">
+        <f t="shared" ca="1" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K11" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B12">
+        <v>34917006</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F12">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B12)</f>
+        <v>4</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ca="1" si="1"/>
+        <v>405</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.32407407407407407</v>
+      </c>
+      <c r="K12" t="s">
+        <v>380</v>
+      </c>
+      <c r="N12" t="s">
+        <v>383</v>
+      </c>
+      <c r="O12">
+        <f>SUM(F2:F16)</f>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B13">
+        <v>37669736</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" t="s">
+        <v>283</v>
+      </c>
+      <c r="E13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F13">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B13)</f>
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13">
+        <f t="shared" ca="1" si="1"/>
+        <v>285</v>
+      </c>
+      <c r="J13" s="10">
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>379</v>
+      </c>
+      <c r="N13" t="s">
+        <v>384</v>
+      </c>
+      <c r="O13">
+        <f>COUNT(B2:B16)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B14">
+        <v>38375955</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E14" t="s">
+        <v>288</v>
+      </c>
+      <c r="F14">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B14)</f>
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14">
+        <f t="shared" ca="1" si="1"/>
+        <v>256</v>
+      </c>
+      <c r="J14" s="10">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B15">
+        <v>40546651</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" t="s">
+        <v>283</v>
+      </c>
+      <c r="E15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B15)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15">
+        <f t="shared" ca="1" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="J15" s="10">
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="K15" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>User Athena</v>
+      </c>
+      <c r="B16">
+        <v>40007087</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" t="s">
+        <v>283</v>
+      </c>
+      <c r="E16" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16">
+        <f>COUNTIF('Results export'!$H$2:$H$202,reporting!B16)</f>
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ca="1" si="1"/>
+        <v>192</v>
+      </c>
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N17" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="O17" s="12"/>
+    </row>
+    <row r="18" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N18" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="19" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N19" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="O19" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N20" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="O20" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N21" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="22" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+    </row>
+    <row r="23" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N23" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="O23" s="12"/>
+    </row>
+    <row r="24" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N24" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="25" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N25" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="O25" s="17" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="26" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N26" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="O26" s="16">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N27" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="O27" s="16">
+        <f>SUMIF($K$2:$K$16,N2,$F$2:$F$16)</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N28" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="O28" s="16">
+        <f>SUMIF($K$2:$K$16,N3,$F$2:$F$16)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="N29" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="O29" s="16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="14:15" x14ac:dyDescent="0.3">
+      <c r="O31" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/september strat simulation/latest(for stakeholder)/strat1254_obs/result_20261007_164841(VN_strat1254_obs_07Oct).xlsx
+++ b/data/september strat simulation/latest(for stakeholder)/strat1254_obs/result_20261007_164841(VN_strat1254_obs_07Oct).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wei.kc\Desktop\Adhoc\03 Sept 2026\data\september strat simulation\latest(for stakeholder)\strat1254_obs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80855E9-F8C8-4A46-9333-47413C9E552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7B608B-032E-4E19-9923-7E4BC380267F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2568" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="408">
   <si>
     <t>traceid</t>
   </si>
@@ -1360,30 +1360,15 @@
     <t>Strategy Observation</t>
   </si>
   <si>
-    <t>True Positives (Accounts)</t>
-  </si>
-  <si>
-    <t>False Positives (Accounts)</t>
-  </si>
-  <si>
     <t>Account Precision</t>
   </si>
   <si>
     <t>Order level</t>
   </si>
   <si>
-    <t>Hit Rate (%)</t>
-  </si>
-  <si>
     <t>Hit Count (Orders)</t>
   </si>
   <si>
-    <t>True Positives (Orders)</t>
-  </si>
-  <si>
-    <t>False Positives (Orders)</t>
-  </si>
-  <si>
     <t>Order Precision</t>
   </si>
   <si>
@@ -1394,17 +1379,51 @@
   </si>
   <si>
     <t>0.00253%</t>
+  </si>
+  <si>
+    <t>Hit Rate (Accounts)</t>
+  </si>
+  <si>
+    <t>0.00064%</t>
+  </si>
+  <si>
+    <t>Hit Count (Accounts)</t>
+  </si>
+  <si>
+    <t>True Positive (Accounts)</t>
+  </si>
+  <si>
+    <t>False Positive (Accounts)</t>
+  </si>
+  <si>
+    <t>True Positive (Orders)</t>
+  </si>
+  <si>
+    <t>False Positive (Orders)</t>
+  </si>
+  <si>
+    <t>Hit Rate (Orders)</t>
+  </si>
+  <si>
+    <t>Simulation</t>
+  </si>
+  <si>
+    <t>81.82% (279 / 341)</t>
+  </si>
+  <si>
+    <t>84.44% (17879 / 21173)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="180" formatCode="0.00000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1434,8 +1453,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1448,8 +1474,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1562,13 +1594,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1588,13 +1687,29 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -13770,10 +13885,10 @@
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
     <col min="15" max="15" width="16.109375" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -14432,106 +14547,157 @@
         <v>379</v>
       </c>
     </row>
-    <row r="17" spans="14:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="14:16" x14ac:dyDescent="0.3">
       <c r="N17" s="12" t="s">
         <v>387</v>
       </c>
       <c r="O17" s="12"/>
     </row>
-    <row r="18" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N18" s="13" t="s">
+    <row r="18" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N18" s="22" t="s">
         <v>388</v>
       </c>
-      <c r="O18" s="14" t="s">
+      <c r="O18" s="23" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="19" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N19" s="15" t="s">
+      <c r="P18" s="22" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N19" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="P19" s="26">
+        <v>5.4258841724890165E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N20" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="O20" s="17">
+        <v>15</v>
+      </c>
+      <c r="P20" s="17">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="21" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N21" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="O21" s="21">
+        <v>12</v>
+      </c>
+      <c r="P21" s="16">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N22" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="O22" s="21">
+        <v>3</v>
+      </c>
+      <c r="P22" s="13">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N23" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="O19" s="16">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N20" s="15" t="s">
+      <c r="O23" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="27"/>
+    </row>
+    <row r="25" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N25" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="O20" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N21" s="15" t="s">
+      <c r="O25" s="12"/>
+      <c r="P25" s="27"/>
+    </row>
+    <row r="26" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N26" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="O26" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="P26" s="24" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="27" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N27" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="O27" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="P27" s="28">
+        <v>2.4479794255497693E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N28" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="O21" s="16" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="22" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-    </row>
-    <row r="23" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N23" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="O23" s="12"/>
-    </row>
-    <row r="24" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N24" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="O24" s="14" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="25" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N25" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="O25" s="17" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="26" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N26" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="O26" s="16">
+      <c r="O28" s="14">
         <v>201</v>
       </c>
-    </row>
-    <row r="27" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N27" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="O27" s="16">
+      <c r="P28" s="29">
+        <v>21173</v>
+      </c>
+    </row>
+    <row r="29" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N29" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="O29" s="14">
         <f>SUMIF($K$2:$K$16,N2,$F$2:$F$16)</f>
         <v>172</v>
       </c>
-    </row>
-    <row r="28" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N28" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="O28" s="16">
+      <c r="P29" s="29">
+        <v>17879</v>
+      </c>
+    </row>
+    <row r="30" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N30" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="O30" s="14">
         <f>SUMIF($K$2:$K$16,N3,$F$2:$F$16)</f>
         <v>29</v>
       </c>
-    </row>
-    <row r="29" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="N29" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="O29" s="16" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="31" spans="14:15" x14ac:dyDescent="0.3">
-      <c r="O31" s="10"/>
+      <c r="P30" s="29">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="31" spans="14:16" x14ac:dyDescent="0.3">
+      <c r="N31" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="P31" s="14" t="s">
+        <v>407</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
